--- a/outputs/unit_economics/юнит_экономика_по_брендам_Коротич.xlsx
+++ b/outputs/unit_economics/юнит_экономика_по_брендам_Коротич.xlsx
@@ -57,7 +57,7 @@
       <color rgb="001F4E78"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +77,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -111,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -125,9 +130,11 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -494,23 +501,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N156"/>
+  <dimension ref="A1:Q156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -523,7 +533,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Цена — рекомендованная под ROI ≥ 30% (где текущий ROI уже ≥30% — цена сохранена). Ставки: комиссия+эквайринг, доставка, налог — факт Ракеты по SKU; ДРР 10%.</t>
+          <t>ТЕК. = текущая цена/ROI из твоего файла цен (Москва Центр). РЕК. = рекомендация под ROI≥30% (если ТЕК. ROI уже ≥30% — цена сохранена, иначе поднята). Жёлтым — где надо поднять цену. Ставки — факт Ракеты; ДРР 10%.</t>
         </is>
       </c>
     </row>
@@ -550,52 +560,67 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Цена до СПП ₽</t>
+          <t>ТЕК. цена до СПП ₽</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>ТЕК. ROI %</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>РЕК. цена до СПП ₽</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Цена с СПП ₽</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>СПП %</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Цена с СПП ₽</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Комиссия+экв ₽</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Доставка ₽</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Налог ₽</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Реклама ДРР ₽</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Маржа ₽/ед</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>ROI %</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>РЕК. ROI %</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Заработок с остатка ₽</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>Статус</t>
         </is>
       </c>
     </row>
@@ -618,6 +643,9 @@
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="5" t="n"/>
       <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -638,31 +666,42 @@
         <v>1387</v>
       </c>
       <c r="F6" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>1387</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>925</v>
+      </c>
+      <c r="I6" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>925</v>
-      </c>
-      <c r="H6" s="7" t="n">
+      <c r="J6" s="7" t="n">
         <v>626</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="K6" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="L6" s="7" t="n">
         <v>86</v>
       </c>
-      <c r="K6" s="7" t="n">
+      <c r="M6" s="7" t="n">
         <v>139</v>
       </c>
-      <c r="L6" s="7" t="n">
+      <c r="N6" s="7" t="n">
         <v>141</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="O6" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="N6" s="7" t="n">
+      <c r="P6" s="7" t="n">
         <v>30763</v>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -687,9 +726,12 @@
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
-      <c r="N7" s="10" t="n">
+      <c r="N7" s="9" t="n"/>
+      <c r="O7" s="9" t="n"/>
+      <c r="P7" s="10" t="n">
         <v>30763</v>
       </c>
+      <c r="Q7" s="9" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -710,6 +752,9 @@
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="5" t="n"/>
       <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -730,31 +775,42 @@
         <v>1387</v>
       </c>
       <c r="F9" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>1387</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>924</v>
+      </c>
+      <c r="I9" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>924</v>
-      </c>
-      <c r="H9" s="7" t="n">
+      <c r="J9" s="7" t="n">
         <v>559</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="K9" s="7" t="n">
         <v>112</v>
       </c>
-      <c r="J9" s="7" t="n">
+      <c r="L9" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="K9" s="7" t="n">
+      <c r="M9" s="7" t="n">
         <v>139</v>
       </c>
-      <c r="L9" s="7" t="n">
+      <c r="N9" s="7" t="n">
         <v>229</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="O9" s="6" t="n">
         <v>85</v>
       </c>
-      <c r="N9" s="7" t="n">
+      <c r="P9" s="7" t="n">
         <v>13530</v>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -776,31 +832,42 @@
         <v>1387</v>
       </c>
       <c r="F10" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>1387</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>925</v>
+      </c>
+      <c r="I10" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>925</v>
-      </c>
-      <c r="H10" s="7" t="n">
+      <c r="J10" s="7" t="n">
         <v>565</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="K10" s="7" t="n">
         <v>134</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="L10" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="K10" s="7" t="n">
+      <c r="M10" s="7" t="n">
         <v>139</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="N10" s="7" t="n">
         <v>160</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="O10" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="N10" s="7" t="n">
+      <c r="P10" s="7" t="n">
         <v>1755</v>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -822,31 +889,42 @@
         <v>920</v>
       </c>
       <c r="F11" s="6" t="n">
+        <v>117</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>920</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>613</v>
+      </c>
+      <c r="I11" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="G11" s="7" t="n">
-        <v>613</v>
-      </c>
-      <c r="H11" s="7" t="n">
+      <c r="J11" s="7" t="n">
         <v>375</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="K11" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="L11" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="K11" s="7" t="n">
+      <c r="M11" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="N11" s="7" t="n">
         <v>176</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="O11" s="6" t="n">
         <v>117</v>
       </c>
-      <c r="N11" s="7" t="n">
+      <c r="P11" s="7" t="n">
         <v>52402</v>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -871,9 +949,12 @@
       <c r="K12" s="9" t="n"/>
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
-      <c r="N12" s="10" t="n">
+      <c r="N12" s="9" t="n"/>
+      <c r="O12" s="9" t="n"/>
+      <c r="P12" s="10" t="n">
         <v>67687</v>
       </c>
+      <c r="Q12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -894,6 +975,9 @@
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="5" t="n"/>
       <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+      <c r="Q13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -914,31 +998,42 @@
         <v>2945</v>
       </c>
       <c r="F14" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>2945</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>1964</v>
+      </c>
+      <c r="I14" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G14" s="7" t="n">
-        <v>1964</v>
-      </c>
-      <c r="H14" s="7" t="n">
+      <c r="J14" s="7" t="n">
         <v>1203</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="K14" s="7" t="n">
         <v>207</v>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="L14" s="7" t="n">
         <v>159</v>
       </c>
-      <c r="K14" s="7" t="n">
+      <c r="M14" s="7" t="n">
         <v>294</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="N14" s="7" t="n">
         <v>354</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="O14" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="N14" s="7" t="n">
+      <c r="P14" s="7" t="n">
         <v>140025</v>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -963,9 +1058,12 @@
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
-      <c r="N15" s="10" t="n">
+      <c r="N15" s="9" t="n"/>
+      <c r="O15" s="9" t="n"/>
+      <c r="P15" s="10" t="n">
         <v>140025</v>
       </c>
+      <c r="Q15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -986,6 +1084,9 @@
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="5" t="n"/>
       <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
+      <c r="Q16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1006,31 +1107,42 @@
         <v>1076</v>
       </c>
       <c r="F17" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>1076</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>717</v>
+      </c>
+      <c r="I17" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="G17" s="7" t="n">
-        <v>717</v>
-      </c>
-      <c r="H17" s="7" t="n">
+      <c r="J17" s="7" t="n">
         <v>470</v>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="K17" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="J17" s="7" t="n">
+      <c r="L17" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="K17" s="7" t="n">
+      <c r="M17" s="7" t="n">
         <v>108</v>
       </c>
-      <c r="L17" s="7" t="n">
+      <c r="N17" s="7" t="n">
         <v>129</v>
       </c>
-      <c r="M17" s="6" t="n">
+      <c r="O17" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="N17" s="7" t="n">
+      <c r="P17" s="7" t="n">
         <v>43939</v>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1052,31 +1164,42 @@
         <v>1855</v>
       </c>
       <c r="F18" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>1855</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>1235</v>
+      </c>
+      <c r="I18" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>1235</v>
-      </c>
-      <c r="H18" s="7" t="n">
+      <c r="J18" s="7" t="n">
         <v>820</v>
       </c>
-      <c r="I18" s="7" t="n">
+      <c r="K18" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="J18" s="7" t="n">
+      <c r="L18" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="K18" s="7" t="n">
+      <c r="M18" s="7" t="n">
         <v>186</v>
       </c>
-      <c r="L18" s="7" t="n">
+      <c r="N18" s="7" t="n">
         <v>242</v>
       </c>
-      <c r="M18" s="6" t="n">
+      <c r="O18" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="N18" s="7" t="n">
+      <c r="P18" s="7" t="n">
         <v>12078</v>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1101,9 +1224,12 @@
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="9" t="n"/>
-      <c r="N19" s="10" t="n">
+      <c r="N19" s="9" t="n"/>
+      <c r="O19" s="9" t="n"/>
+      <c r="P19" s="10" t="n">
         <v>56017</v>
       </c>
+      <c r="Q19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1124,6 +1250,9 @@
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="5" t="n"/>
       <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1144,31 +1273,42 @@
         <v>921</v>
       </c>
       <c r="F21" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>921</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>614</v>
+      </c>
+      <c r="I21" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G21" s="7" t="n">
-        <v>614</v>
-      </c>
-      <c r="H21" s="7" t="n">
+      <c r="J21" s="7" t="n">
         <v>407</v>
       </c>
-      <c r="I21" s="7" t="n">
+      <c r="K21" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="J21" s="7" t="n">
+      <c r="L21" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="K21" s="7" t="n">
+      <c r="M21" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="L21" s="7" t="n">
+      <c r="N21" s="7" t="n">
         <v>156</v>
       </c>
-      <c r="M21" s="6" t="n">
+      <c r="O21" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="N21" s="7" t="n">
+      <c r="P21" s="7" t="n">
         <v>997272</v>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1190,31 +1330,42 @@
         <v>766</v>
       </c>
       <c r="F22" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>766</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>510</v>
+      </c>
+      <c r="I22" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="G22" s="7" t="n">
-        <v>510</v>
-      </c>
-      <c r="H22" s="7" t="n">
+      <c r="J22" s="7" t="n">
         <v>339</v>
       </c>
-      <c r="I22" s="7" t="n">
+      <c r="K22" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="L22" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="K22" s="7" t="n">
+      <c r="M22" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="L22" s="7" t="n">
+      <c r="N22" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="M22" s="6" t="n">
+      <c r="O22" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="N22" s="7" t="n">
+      <c r="P22" s="7" t="n">
         <v>17388</v>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1236,31 +1387,42 @@
         <v>1233</v>
       </c>
       <c r="F23" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>1233</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>822</v>
+      </c>
+      <c r="I23" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G23" s="7" t="n">
-        <v>822</v>
-      </c>
-      <c r="H23" s="7" t="n">
+      <c r="J23" s="7" t="n">
         <v>545</v>
       </c>
-      <c r="I23" s="7" t="n">
+      <c r="K23" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="J23" s="7" t="n">
+      <c r="L23" s="7" t="n">
         <v>76</v>
       </c>
-      <c r="K23" s="7" t="n">
+      <c r="M23" s="7" t="n">
         <v>123</v>
       </c>
-      <c r="L23" s="7" t="n">
+      <c r="N23" s="7" t="n">
         <v>221</v>
       </c>
-      <c r="M23" s="6" t="n">
+      <c r="O23" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="N23" s="7" t="n">
+      <c r="P23" s="7" t="n">
         <v>11703</v>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1282,31 +1444,42 @@
         <v>1233</v>
       </c>
       <c r="F24" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>1233</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>822</v>
+      </c>
+      <c r="I24" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G24" s="7" t="n">
-        <v>822</v>
-      </c>
-      <c r="H24" s="7" t="n">
+      <c r="J24" s="7" t="n">
         <v>545</v>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="K24" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="J24" s="7" t="n">
+      <c r="L24" s="7" t="n">
         <v>76</v>
       </c>
-      <c r="K24" s="7" t="n">
+      <c r="M24" s="7" t="n">
         <v>123</v>
       </c>
-      <c r="L24" s="7" t="n">
+      <c r="N24" s="7" t="n">
         <v>195</v>
       </c>
-      <c r="M24" s="6" t="n">
+      <c r="O24" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="N24" s="7" t="n">
+      <c r="P24" s="7" t="n">
         <v>38513</v>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1328,31 +1501,42 @@
         <v>1076</v>
       </c>
       <c r="F25" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>1076</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>717</v>
+      </c>
+      <c r="I25" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="G25" s="7" t="n">
-        <v>717</v>
-      </c>
-      <c r="H25" s="7" t="n">
+      <c r="J25" s="7" t="n">
         <v>476</v>
       </c>
-      <c r="I25" s="7" t="n">
+      <c r="K25" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="J25" s="7" t="n">
+      <c r="L25" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="K25" s="7" t="n">
+      <c r="M25" s="7" t="n">
         <v>108</v>
       </c>
-      <c r="L25" s="7" t="n">
+      <c r="N25" s="7" t="n">
         <v>137</v>
       </c>
-      <c r="M25" s="6" t="n">
+      <c r="O25" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="N25" s="7" t="n">
+      <c r="P25" s="7" t="n">
         <v>95945</v>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1374,31 +1558,42 @@
         <v>1077</v>
       </c>
       <c r="F26" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>1077</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>718</v>
+      </c>
+      <c r="I26" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G26" s="7" t="n">
-        <v>718</v>
-      </c>
-      <c r="H26" s="7" t="n">
+      <c r="J26" s="7" t="n">
         <v>484</v>
       </c>
-      <c r="I26" s="7" t="n">
+      <c r="K26" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="J26" s="7" t="n">
+      <c r="L26" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="K26" s="7" t="n">
+      <c r="M26" s="7" t="n">
         <v>108</v>
       </c>
-      <c r="L26" s="7" t="n">
+      <c r="N26" s="7" t="n">
         <v>104</v>
       </c>
-      <c r="M26" s="6" t="n">
+      <c r="O26" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="N26" s="7" t="n">
+      <c r="P26" s="7" t="n">
         <v>41577</v>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1420,31 +1615,42 @@
         <v>1076</v>
       </c>
       <c r="F27" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>1076</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>718</v>
+      </c>
+      <c r="I27" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G27" s="7" t="n">
-        <v>718</v>
-      </c>
-      <c r="H27" s="7" t="n">
+      <c r="J27" s="7" t="n">
         <v>476</v>
       </c>
-      <c r="I27" s="7" t="n">
+      <c r="K27" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="J27" s="7" t="n">
+      <c r="L27" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="K27" s="7" t="n">
+      <c r="M27" s="7" t="n">
         <v>108</v>
       </c>
-      <c r="L27" s="7" t="n">
+      <c r="N27" s="7" t="n">
         <v>149</v>
       </c>
-      <c r="M27" s="6" t="n">
+      <c r="O27" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="N27" s="7" t="n">
+      <c r="P27" s="7" t="n">
         <v>1789</v>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1466,31 +1672,42 @@
         <v>1387</v>
       </c>
       <c r="F28" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>1387</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>924</v>
+      </c>
+      <c r="I28" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="G28" s="7" t="n">
-        <v>924</v>
-      </c>
-      <c r="H28" s="7" t="n">
+      <c r="J28" s="7" t="n">
         <v>613</v>
       </c>
-      <c r="I28" s="7" t="n">
+      <c r="K28" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="J28" s="7" t="n">
+      <c r="L28" s="7" t="n">
         <v>83</v>
       </c>
-      <c r="K28" s="7" t="n">
+      <c r="M28" s="7" t="n">
         <v>139</v>
       </c>
-      <c r="L28" s="7" t="n">
+      <c r="N28" s="7" t="n">
         <v>203</v>
       </c>
-      <c r="M28" s="6" t="n">
+      <c r="O28" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="N28" s="7" t="n">
+      <c r="P28" s="7" t="n">
         <v>4667</v>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1512,31 +1729,42 @@
         <v>1077</v>
       </c>
       <c r="F29" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>1077</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>718</v>
+      </c>
+      <c r="I29" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G29" s="7" t="n">
-        <v>718</v>
-      </c>
-      <c r="H29" s="7" t="n">
+      <c r="J29" s="7" t="n">
         <v>480</v>
       </c>
-      <c r="I29" s="7" t="n">
+      <c r="K29" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="J29" s="7" t="n">
+      <c r="L29" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="K29" s="7" t="n">
+      <c r="M29" s="7" t="n">
         <v>108</v>
       </c>
-      <c r="L29" s="7" t="n">
+      <c r="N29" s="7" t="n">
         <v>116</v>
       </c>
-      <c r="M29" s="6" t="n">
+      <c r="O29" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="N29" s="7" t="n">
+      <c r="P29" s="7" t="n">
         <v>23261</v>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1558,77 +1786,99 @@
         <v>1076</v>
       </c>
       <c r="F30" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>1076</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>718</v>
+      </c>
+      <c r="I30" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G30" s="7" t="n">
-        <v>718</v>
-      </c>
-      <c r="H30" s="7" t="n">
+      <c r="J30" s="7" t="n">
         <v>485</v>
       </c>
-      <c r="I30" s="7" t="n">
+      <c r="K30" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="J30" s="7" t="n">
+      <c r="L30" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="K30" s="7" t="n">
+      <c r="M30" s="7" t="n">
         <v>108</v>
       </c>
-      <c r="L30" s="7" t="n">
+      <c r="N30" s="7" t="n">
         <v>114</v>
       </c>
-      <c r="M30" s="6" t="n">
+      <c r="O30" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="N30" s="7" t="n">
+      <c r="P30" s="7" t="n">
         <v>45630</v>
       </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>ENOUGH - Premium Ultra X10 Cover Up Collagen Foundation [Tone 13] / Тональный крем с коллагеном 13 тон</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="11" t="n">
         <v>170198835</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="12" t="n">
         <v>315.45</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="11" t="n">
         <v>1000</v>
       </c>
-      <c r="E31" s="7" t="n">
+      <c r="E31" s="12" t="n">
+        <v>1076</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="G31" s="12" t="n">
         <v>1163</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="H31" s="12" t="n">
+        <v>776</v>
+      </c>
+      <c r="I31" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G31" s="7" t="n">
-        <v>776</v>
-      </c>
-      <c r="H31" s="7" t="n">
+      <c r="J31" s="12" t="n">
         <v>533</v>
       </c>
-      <c r="I31" s="7" t="n">
+      <c r="K31" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="J31" s="7" t="n">
+      <c r="L31" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="K31" s="7" t="n">
+      <c r="M31" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="L31" s="7" t="n">
+      <c r="N31" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="M31" s="6" t="n">
+      <c r="O31" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N31" s="7" t="n">
+      <c r="P31" s="12" t="n">
         <v>94635</v>
+      </c>
+      <c r="Q31" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1650,31 +1900,42 @@
         <v>1233</v>
       </c>
       <c r="F32" s="6" t="n">
+        <v>147</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>1233</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>822</v>
+      </c>
+      <c r="I32" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G32" s="7" t="n">
-        <v>822</v>
-      </c>
-      <c r="H32" s="7" t="n">
+      <c r="J32" s="7" t="n">
         <v>544</v>
       </c>
-      <c r="I32" s="7" t="n">
+      <c r="K32" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="J32" s="7" t="n">
+      <c r="L32" s="7" t="n">
         <v>74</v>
       </c>
-      <c r="K32" s="7" t="n">
+      <c r="M32" s="7" t="n">
         <v>123</v>
       </c>
-      <c r="L32" s="7" t="n">
+      <c r="N32" s="7" t="n">
         <v>270</v>
       </c>
-      <c r="M32" s="6" t="n">
+      <c r="O32" s="6" t="n">
         <v>147</v>
       </c>
-      <c r="N32" s="7" t="n">
+      <c r="P32" s="7" t="n">
         <v>94865</v>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1696,31 +1957,42 @@
         <v>1233</v>
       </c>
       <c r="F33" s="6" t="n">
+        <v>147</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>1233</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>822</v>
+      </c>
+      <c r="I33" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G33" s="7" t="n">
-        <v>822</v>
-      </c>
-      <c r="H33" s="7" t="n">
+      <c r="J33" s="7" t="n">
         <v>545</v>
       </c>
-      <c r="I33" s="7" t="n">
+      <c r="K33" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="J33" s="7" t="n">
+      <c r="L33" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="K33" s="7" t="n">
+      <c r="M33" s="7" t="n">
         <v>123</v>
       </c>
-      <c r="L33" s="7" t="n">
+      <c r="N33" s="7" t="n">
         <v>269</v>
       </c>
-      <c r="M33" s="6" t="n">
+      <c r="O33" s="6" t="n">
         <v>147</v>
       </c>
-      <c r="N33" s="7" t="n">
+      <c r="P33" s="7" t="n">
         <v>145105</v>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1742,31 +2014,42 @@
         <v>1233</v>
       </c>
       <c r="F34" s="6" t="n">
+        <v>138</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>1233</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>822</v>
+      </c>
+      <c r="I34" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G34" s="7" t="n">
-        <v>822</v>
-      </c>
-      <c r="H34" s="7" t="n">
+      <c r="J34" s="7" t="n">
         <v>545</v>
       </c>
-      <c r="I34" s="7" t="n">
+      <c r="K34" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="J34" s="7" t="n">
+      <c r="L34" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="K34" s="7" t="n">
+      <c r="M34" s="7" t="n">
         <v>123</v>
       </c>
-      <c r="L34" s="7" t="n">
+      <c r="N34" s="7" t="n">
         <v>252</v>
       </c>
-      <c r="M34" s="6" t="n">
+      <c r="O34" s="6" t="n">
         <v>138</v>
       </c>
-      <c r="N34" s="7" t="n">
+      <c r="P34" s="7" t="n">
         <v>174950</v>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1788,31 +2071,42 @@
         <v>792</v>
       </c>
       <c r="F35" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>792</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>527</v>
+      </c>
+      <c r="I35" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="G35" s="7" t="n">
-        <v>527</v>
-      </c>
-      <c r="H35" s="7" t="n">
+      <c r="J35" s="7" t="n">
         <v>350</v>
       </c>
-      <c r="I35" s="7" t="n">
+      <c r="K35" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="J35" s="7" t="n">
+      <c r="L35" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="K35" s="7" t="n">
+      <c r="M35" s="7" t="n">
         <v>79</v>
       </c>
-      <c r="L35" s="7" t="n">
+      <c r="N35" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="M35" s="6" t="n">
+      <c r="O35" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="N35" s="7" t="n">
+      <c r="P35" s="7" t="n">
         <v>47582</v>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1837,9 +2131,12 @@
       <c r="K36" s="9" t="n"/>
       <c r="L36" s="9" t="n"/>
       <c r="M36" s="9" t="n"/>
-      <c r="N36" s="10" t="n">
+      <c r="N36" s="9" t="n"/>
+      <c r="O36" s="9" t="n"/>
+      <c r="P36" s="10" t="n">
         <v>1834882</v>
       </c>
+      <c r="Q36" s="9" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -1860,6 +2157,9 @@
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="5" t="n"/>
       <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
+      <c r="Q37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -1880,31 +2180,42 @@
         <v>1542</v>
       </c>
       <c r="F38" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>1542</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>1029</v>
+      </c>
+      <c r="I38" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G38" s="7" t="n">
-        <v>1029</v>
-      </c>
-      <c r="H38" s="7" t="n">
+      <c r="J38" s="7" t="n">
         <v>683</v>
       </c>
-      <c r="I38" s="7" t="n">
+      <c r="K38" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="J38" s="7" t="n">
+      <c r="L38" s="7" t="n">
         <v>83</v>
       </c>
-      <c r="K38" s="7" t="n">
+      <c r="M38" s="7" t="n">
         <v>154</v>
       </c>
-      <c r="L38" s="7" t="n">
+      <c r="N38" s="7" t="n">
         <v>211</v>
       </c>
-      <c r="M38" s="6" t="n">
+      <c r="O38" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="N38" s="7" t="n">
+      <c r="P38" s="7" t="n">
         <v>1518306</v>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1926,77 +2237,95 @@
         <v>1232</v>
       </c>
       <c r="F39" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>1232</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>821</v>
+      </c>
+      <c r="I39" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="G39" s="7" t="n">
-        <v>821</v>
-      </c>
-      <c r="H39" s="7" t="n">
+      <c r="J39" s="7" t="n">
         <v>545</v>
       </c>
-      <c r="I39" s="7" t="n">
+      <c r="K39" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="J39" s="7" t="n">
+      <c r="L39" s="7" t="n">
         <v>74</v>
       </c>
-      <c r="K39" s="7" t="n">
+      <c r="M39" s="7" t="n">
         <v>123</v>
       </c>
-      <c r="L39" s="7" t="n">
+      <c r="N39" s="7" t="n">
         <v>146</v>
       </c>
-      <c r="M39" s="6" t="n">
+      <c r="O39" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="N39" s="7" t="n">
+      <c r="P39" s="7" t="n">
         <v>9365</v>
       </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>ETUDE - Baking Powder Crunch Pore Scrub [24*7ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="11" t="n">
         <v>154160085</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="12" t="n">
         <v>389.99</v>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E40" s="7" t="n">
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="11" t="n"/>
+      <c r="G40" s="12" t="n">
         <v>1472</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="H40" s="12" t="n">
+        <v>986</v>
+      </c>
+      <c r="I40" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="G40" s="7" t="n">
-        <v>986</v>
-      </c>
-      <c r="H40" s="7" t="n">
+      <c r="J40" s="12" t="n">
         <v>654</v>
       </c>
-      <c r="I40" s="7" t="n">
+      <c r="K40" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="J40" s="7" t="n">
+      <c r="L40" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="K40" s="7" t="n">
+      <c r="M40" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="L40" s="7" t="n">
+      <c r="N40" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="M40" s="6" t="n">
+      <c r="O40" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N40" s="7" t="n">
+      <c r="P40" s="12" t="n">
         <v>234</v>
+      </c>
+      <c r="Q40" s="11" t="inlineStr">
+        <is>
+          <t>Поднять до ROI30 (нет цены)</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -2021,9 +2350,12 @@
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n"/>
       <c r="M41" s="9" t="n"/>
-      <c r="N41" s="10" t="n">
+      <c r="N41" s="9" t="n"/>
+      <c r="O41" s="9" t="n"/>
+      <c r="P41" s="10" t="n">
         <v>1527905</v>
       </c>
+      <c r="Q41" s="9" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -2044,6 +2376,9 @@
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="5" t="n"/>
       <c r="N42" s="5" t="n"/>
+      <c r="O42" s="5" t="n"/>
+      <c r="P42" s="5" t="n"/>
+      <c r="Q42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -2064,31 +2399,42 @@
         <v>1515</v>
       </c>
       <c r="F43" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G43" s="7" t="n">
+        <v>1515</v>
+      </c>
+      <c r="H43" s="7" t="n">
+        <v>1011</v>
+      </c>
+      <c r="I43" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G43" s="7" t="n">
-        <v>1011</v>
-      </c>
-      <c r="H43" s="7" t="n">
+      <c r="J43" s="7" t="n">
         <v>670</v>
       </c>
-      <c r="I43" s="7" t="n">
+      <c r="K43" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="J43" s="7" t="n">
+      <c r="L43" s="7" t="n">
         <v>83</v>
       </c>
-      <c r="K43" s="7" t="n">
+      <c r="M43" s="7" t="n">
         <v>152</v>
       </c>
-      <c r="L43" s="7" t="n">
+      <c r="N43" s="7" t="n">
         <v>208</v>
       </c>
-      <c r="M43" s="6" t="n">
+      <c r="O43" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="N43" s="7" t="n">
+      <c r="P43" s="7" t="n">
         <v>1260595</v>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -2110,31 +2456,42 @@
         <v>1620</v>
       </c>
       <c r="F44" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>1620</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>1081</v>
+      </c>
+      <c r="I44" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G44" s="7" t="n">
-        <v>1081</v>
-      </c>
-      <c r="H44" s="7" t="n">
+      <c r="J44" s="7" t="n">
         <v>659</v>
       </c>
-      <c r="I44" s="7" t="n">
+      <c r="K44" s="7" t="n">
         <v>136</v>
       </c>
-      <c r="J44" s="7" t="n">
+      <c r="L44" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="K44" s="7" t="n">
+      <c r="M44" s="7" t="n">
         <v>162</v>
       </c>
-      <c r="L44" s="7" t="n">
+      <c r="N44" s="7" t="n">
         <v>175</v>
       </c>
-      <c r="M44" s="6" t="n">
+      <c r="O44" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="N44" s="7" t="n">
+      <c r="P44" s="7" t="n">
         <v>561178</v>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -2156,31 +2513,42 @@
         <v>2166</v>
       </c>
       <c r="F45" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>2166</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>1445</v>
+      </c>
+      <c r="I45" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G45" s="7" t="n">
-        <v>1445</v>
-      </c>
-      <c r="H45" s="7" t="n">
+      <c r="J45" s="7" t="n">
         <v>957</v>
       </c>
-      <c r="I45" s="7" t="n">
+      <c r="K45" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="J45" s="7" t="n">
+      <c r="L45" s="7" t="n">
         <v>114</v>
       </c>
-      <c r="K45" s="7" t="n">
+      <c r="M45" s="7" t="n">
         <v>217</v>
       </c>
-      <c r="L45" s="7" t="n">
+      <c r="N45" s="7" t="n">
         <v>396</v>
       </c>
-      <c r="M45" s="6" t="n">
+      <c r="O45" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="N45" s="7" t="n">
+      <c r="P45" s="7" t="n">
         <v>337247</v>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -2202,77 +2570,99 @@
         <v>1233</v>
       </c>
       <c r="F46" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>1233</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>822</v>
+      </c>
+      <c r="I46" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G46" s="7" t="n">
-        <v>822</v>
-      </c>
-      <c r="H46" s="7" t="n">
+      <c r="J46" s="7" t="n">
         <v>545</v>
       </c>
-      <c r="I46" s="7" t="n">
+      <c r="K46" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="J46" s="7" t="n">
+      <c r="L46" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="K46" s="7" t="n">
+      <c r="M46" s="7" t="n">
         <v>123</v>
       </c>
-      <c r="L46" s="7" t="n">
+      <c r="N46" s="7" t="n">
         <v>133</v>
       </c>
-      <c r="M46" s="6" t="n">
+      <c r="O46" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="N46" s="7" t="n">
+      <c r="P46" s="7" t="n">
         <v>111380</v>
       </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
         </is>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="11" t="n">
         <v>419630142</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="12" t="n">
         <v>390.46</v>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="D47" s="11" t="n">
         <v>821</v>
       </c>
-      <c r="E47" s="7" t="n">
+      <c r="E47" s="12" t="n">
+        <v>1387</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="G47" s="12" t="n">
         <v>1403</v>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="H47" s="12" t="n">
+        <v>936</v>
+      </c>
+      <c r="I47" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G47" s="7" t="n">
-        <v>936</v>
-      </c>
-      <c r="H47" s="7" t="n">
+      <c r="J47" s="12" t="n">
         <v>622</v>
       </c>
-      <c r="I47" s="7" t="n">
+      <c r="K47" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="J47" s="7" t="n">
+      <c r="L47" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="K47" s="7" t="n">
+      <c r="M47" s="12" t="n">
         <v>140</v>
       </c>
-      <c r="L47" s="7" t="n">
+      <c r="N47" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="M47" s="6" t="n">
+      <c r="O47" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N47" s="7" t="n">
+      <c r="P47" s="12" t="n">
         <v>96170</v>
+      </c>
+      <c r="Q47" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -2294,31 +2684,42 @@
         <v>1543</v>
       </c>
       <c r="F48" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>1029</v>
+      </c>
+      <c r="I48" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G48" s="7" t="n">
-        <v>1029</v>
-      </c>
-      <c r="H48" s="7" t="n">
+      <c r="J48" s="7" t="n">
         <v>628</v>
       </c>
-      <c r="I48" s="7" t="n">
+      <c r="K48" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="J48" s="7" t="n">
+      <c r="L48" s="7" t="n">
         <v>88</v>
       </c>
-      <c r="K48" s="7" t="n">
+      <c r="M48" s="7" t="n">
         <v>154</v>
       </c>
-      <c r="L48" s="7" t="n">
+      <c r="N48" s="7" t="n">
         <v>172</v>
       </c>
-      <c r="M48" s="6" t="n">
+      <c r="O48" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="N48" s="7" t="n">
+      <c r="P48" s="7" t="n">
         <v>394789</v>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -2340,31 +2741,42 @@
         <v>1543</v>
       </c>
       <c r="F49" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>1029</v>
+      </c>
+      <c r="I49" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G49" s="7" t="n">
-        <v>1029</v>
-      </c>
-      <c r="H49" s="7" t="n">
+      <c r="J49" s="7" t="n">
         <v>635</v>
       </c>
-      <c r="I49" s="7" t="n">
+      <c r="K49" s="7" t="n">
         <v>84</v>
       </c>
-      <c r="J49" s="7" t="n">
+      <c r="L49" s="7" t="n">
         <v>93</v>
       </c>
-      <c r="K49" s="7" t="n">
+      <c r="M49" s="7" t="n">
         <v>154</v>
       </c>
-      <c r="L49" s="7" t="n">
+      <c r="N49" s="7" t="n">
         <v>179</v>
       </c>
-      <c r="M49" s="6" t="n">
+      <c r="O49" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="N49" s="7" t="n">
+      <c r="P49" s="7" t="n">
         <v>605425</v>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -2386,31 +2798,42 @@
         <v>1076</v>
       </c>
       <c r="F50" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>1076</v>
+      </c>
+      <c r="H50" s="7" t="n">
+        <v>718</v>
+      </c>
+      <c r="I50" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G50" s="7" t="n">
-        <v>718</v>
-      </c>
-      <c r="H50" s="7" t="n">
+      <c r="J50" s="7" t="n">
         <v>477</v>
       </c>
-      <c r="I50" s="7" t="n">
+      <c r="K50" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="J50" s="7" t="n">
+      <c r="L50" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="K50" s="7" t="n">
+      <c r="M50" s="7" t="n">
         <v>108</v>
       </c>
-      <c r="L50" s="7" t="n">
+      <c r="N50" s="7" t="n">
         <v>151</v>
       </c>
-      <c r="M50" s="6" t="n">
+      <c r="O50" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="N50" s="7" t="n">
+      <c r="P50" s="7" t="n">
         <v>23543</v>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -2432,31 +2855,42 @@
         <v>2010</v>
       </c>
       <c r="F51" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="G51" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H51" s="7" t="n">
+        <v>1341</v>
+      </c>
+      <c r="I51" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G51" s="7" t="n">
-        <v>1341</v>
-      </c>
-      <c r="H51" s="7" t="n">
+      <c r="J51" s="7" t="n">
         <v>892</v>
       </c>
-      <c r="I51" s="7" t="n">
+      <c r="K51" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="J51" s="7" t="n">
+      <c r="L51" s="7" t="n">
         <v>112</v>
       </c>
-      <c r="K51" s="7" t="n">
+      <c r="M51" s="7" t="n">
         <v>201</v>
       </c>
-      <c r="L51" s="7" t="n">
+      <c r="N51" s="7" t="n">
         <v>271</v>
       </c>
-      <c r="M51" s="6" t="n">
+      <c r="O51" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="N51" s="7" t="n">
+      <c r="P51" s="7" t="n">
         <v>64837</v>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -2478,31 +2912,42 @@
         <v>920</v>
       </c>
       <c r="F52" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>920</v>
+      </c>
+      <c r="H52" s="7" t="n">
+        <v>613</v>
+      </c>
+      <c r="I52" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="G52" s="7" t="n">
-        <v>613</v>
-      </c>
-      <c r="H52" s="7" t="n">
+      <c r="J52" s="7" t="n">
         <v>410</v>
       </c>
-      <c r="I52" s="7" t="n">
+      <c r="K52" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="J52" s="7" t="n">
+      <c r="L52" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="K52" s="7" t="n">
+      <c r="M52" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="L52" s="7" t="n">
+      <c r="N52" s="7" t="n">
         <v>152</v>
       </c>
-      <c r="M52" s="6" t="n">
+      <c r="O52" s="6" t="n">
         <v>94</v>
       </c>
-      <c r="N52" s="7" t="n">
+      <c r="P52" s="7" t="n">
         <v>57883</v>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -2527,9 +2972,12 @@
       <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="n"/>
       <c r="M53" s="9" t="n"/>
-      <c r="N53" s="10" t="n">
+      <c r="N53" s="9" t="n"/>
+      <c r="O53" s="9" t="n"/>
+      <c r="P53" s="10" t="n">
         <v>3513047</v>
       </c>
+      <c r="Q53" s="9" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -2550,51 +2998,65 @@
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="5" t="n"/>
       <c r="N54" s="5" t="n"/>
+      <c r="O54" s="5" t="n"/>
+      <c r="P54" s="5" t="n"/>
+      <c r="Q54" s="5" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
         </is>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="11" t="n">
         <v>207466866</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="12" t="n">
         <v>770.48</v>
       </c>
-      <c r="D55" s="6" t="n">
+      <c r="D55" s="11" t="n">
         <v>930</v>
       </c>
-      <c r="E55" s="7" t="n">
+      <c r="E55" s="12" t="n">
+        <v>2477</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="G55" s="12" t="n">
         <v>2661</v>
       </c>
-      <c r="F55" s="6" t="n">
+      <c r="H55" s="12" t="n">
+        <v>1775</v>
+      </c>
+      <c r="I55" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G55" s="7" t="n">
-        <v>1775</v>
-      </c>
-      <c r="H55" s="7" t="n">
+      <c r="J55" s="12" t="n">
         <v>1183</v>
       </c>
-      <c r="I55" s="7" t="n">
+      <c r="K55" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="J55" s="7" t="n">
+      <c r="L55" s="12" t="n">
         <v>155</v>
       </c>
-      <c r="K55" s="7" t="n">
+      <c r="M55" s="12" t="n">
         <v>266</v>
       </c>
-      <c r="L55" s="7" t="n">
+      <c r="N55" s="12" t="n">
         <v>231</v>
       </c>
-      <c r="M55" s="6" t="n">
+      <c r="O55" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N55" s="7" t="n">
+      <c r="P55" s="12" t="n">
         <v>214964</v>
+      </c>
+      <c r="Q55" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -2619,9 +3081,12 @@
       <c r="K56" s="9" t="n"/>
       <c r="L56" s="9" t="n"/>
       <c r="M56" s="9" t="n"/>
-      <c r="N56" s="10" t="n">
+      <c r="N56" s="9" t="n"/>
+      <c r="O56" s="9" t="n"/>
+      <c r="P56" s="10" t="n">
         <v>214964</v>
       </c>
+      <c r="Q56" s="9" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -2642,6 +3107,9 @@
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="5" t="n"/>
       <c r="N57" s="5" t="n"/>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="5" t="n"/>
+      <c r="Q57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -2662,31 +3130,42 @@
         <v>921</v>
       </c>
       <c r="F58" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>921</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>614</v>
+      </c>
+      <c r="I58" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G58" s="7" t="n">
-        <v>614</v>
-      </c>
-      <c r="H58" s="7" t="n">
+      <c r="J58" s="7" t="n">
         <v>407</v>
       </c>
-      <c r="I58" s="7" t="n">
+      <c r="K58" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="J58" s="7" t="n">
+      <c r="L58" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="K58" s="7" t="n">
+      <c r="M58" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="L58" s="7" t="n">
+      <c r="N58" s="7" t="n">
         <v>118</v>
       </c>
-      <c r="M58" s="6" t="n">
+      <c r="O58" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="N58" s="7" t="n">
+      <c r="P58" s="7" t="n">
         <v>844158</v>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -2708,31 +3187,42 @@
         <v>766</v>
       </c>
       <c r="F59" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G59" s="7" t="n">
+        <v>766</v>
+      </c>
+      <c r="H59" s="7" t="n">
+        <v>510</v>
+      </c>
+      <c r="I59" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="G59" s="7" t="n">
-        <v>510</v>
-      </c>
-      <c r="H59" s="7" t="n">
+      <c r="J59" s="7" t="n">
         <v>339</v>
       </c>
-      <c r="I59" s="7" t="n">
+      <c r="K59" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="J59" s="7" t="n">
+      <c r="L59" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="K59" s="7" t="n">
+      <c r="M59" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="L59" s="7" t="n">
+      <c r="N59" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="M59" s="6" t="n">
+      <c r="O59" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="N59" s="7" t="n">
+      <c r="P59" s="7" t="n">
         <v>56306</v>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -2754,31 +3244,42 @@
         <v>920</v>
       </c>
       <c r="F60" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>920</v>
+      </c>
+      <c r="H60" s="7" t="n">
+        <v>613</v>
+      </c>
+      <c r="I60" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="G60" s="7" t="n">
-        <v>613</v>
-      </c>
-      <c r="H60" s="7" t="n">
+      <c r="J60" s="7" t="n">
         <v>406</v>
       </c>
-      <c r="I60" s="7" t="n">
+      <c r="K60" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="J60" s="7" t="n">
+      <c r="L60" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="K60" s="7" t="n">
+      <c r="M60" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="L60" s="7" t="n">
+      <c r="N60" s="7" t="n">
         <v>123</v>
       </c>
-      <c r="M60" s="6" t="n">
+      <c r="O60" s="6" t="n">
         <v>61</v>
       </c>
-      <c r="N60" s="7" t="n">
+      <c r="P60" s="7" t="n">
         <v>197292</v>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -2803,9 +3304,12 @@
       <c r="K61" s="9" t="n"/>
       <c r="L61" s="9" t="n"/>
       <c r="M61" s="9" t="n"/>
-      <c r="N61" s="10" t="n">
+      <c r="N61" s="9" t="n"/>
+      <c r="O61" s="9" t="n"/>
+      <c r="P61" s="10" t="n">
         <v>1097756</v>
       </c>
+      <c r="Q61" s="9" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -2826,6 +3330,9 @@
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="5" t="n"/>
       <c r="N62" s="5" t="n"/>
+      <c r="O62" s="5" t="n"/>
+      <c r="P62" s="5" t="n"/>
+      <c r="Q62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -2846,31 +3353,42 @@
         <v>1387</v>
       </c>
       <c r="F63" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="G63" s="7" t="n">
+        <v>1387</v>
+      </c>
+      <c r="H63" s="7" t="n">
+        <v>925</v>
+      </c>
+      <c r="I63" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G63" s="7" t="n">
-        <v>925</v>
-      </c>
-      <c r="H63" s="7" t="n">
+      <c r="J63" s="7" t="n">
         <v>571</v>
       </c>
-      <c r="I63" s="7" t="n">
+      <c r="K63" s="7" t="n">
         <v>114</v>
       </c>
-      <c r="J63" s="7" t="n">
+      <c r="L63" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="K63" s="7" t="n">
+      <c r="M63" s="7" t="n">
         <v>139</v>
       </c>
-      <c r="L63" s="7" t="n">
+      <c r="N63" s="7" t="n">
         <v>154</v>
       </c>
-      <c r="M63" s="6" t="n">
+      <c r="O63" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="N63" s="7" t="n">
+      <c r="P63" s="7" t="n">
         <v>200279</v>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -2895,9 +3413,12 @@
       <c r="K64" s="9" t="n"/>
       <c r="L64" s="9" t="n"/>
       <c r="M64" s="9" t="n"/>
-      <c r="N64" s="10" t="n">
+      <c r="N64" s="9" t="n"/>
+      <c r="O64" s="9" t="n"/>
+      <c r="P64" s="10" t="n">
         <v>200279</v>
       </c>
+      <c r="Q64" s="9" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -2918,6 +3439,9 @@
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="5" t="n"/>
       <c r="N65" s="5" t="n"/>
+      <c r="O65" s="5" t="n"/>
+      <c r="P65" s="5" t="n"/>
+      <c r="Q65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -2938,31 +3462,42 @@
         <v>1232</v>
       </c>
       <c r="F66" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>1232</v>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>821</v>
+      </c>
+      <c r="I66" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="G66" s="7" t="n">
-        <v>821</v>
-      </c>
-      <c r="H66" s="7" t="n">
+      <c r="J66" s="7" t="n">
         <v>545</v>
       </c>
-      <c r="I66" s="7" t="n">
+      <c r="K66" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="J66" s="7" t="n">
+      <c r="L66" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="K66" s="7" t="n">
+      <c r="M66" s="7" t="n">
         <v>123</v>
       </c>
-      <c r="L66" s="7" t="n">
+      <c r="N66" s="7" t="n">
         <v>157</v>
       </c>
-      <c r="M66" s="6" t="n">
+      <c r="O66" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="N66" s="7" t="n">
+      <c r="P66" s="7" t="n">
         <v>177931</v>
+      </c>
+      <c r="Q66" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -2984,31 +3519,42 @@
         <v>1232</v>
       </c>
       <c r="F67" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G67" s="7" t="n">
+        <v>1232</v>
+      </c>
+      <c r="H67" s="7" t="n">
+        <v>821</v>
+      </c>
+      <c r="I67" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="G67" s="7" t="n">
-        <v>821</v>
-      </c>
-      <c r="H67" s="7" t="n">
+      <c r="J67" s="7" t="n">
         <v>545</v>
       </c>
-      <c r="I67" s="7" t="n">
+      <c r="K67" s="7" t="n">
         <v>120</v>
       </c>
-      <c r="J67" s="7" t="n">
+      <c r="L67" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="K67" s="7" t="n">
+      <c r="M67" s="7" t="n">
         <v>123</v>
       </c>
-      <c r="L67" s="7" t="n">
+      <c r="N67" s="7" t="n">
         <v>112</v>
       </c>
-      <c r="M67" s="6" t="n">
+      <c r="O67" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="N67" s="7" t="n">
+      <c r="P67" s="7" t="n">
         <v>132363</v>
+      </c>
+      <c r="Q67" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -3030,31 +3576,42 @@
         <v>1232</v>
       </c>
       <c r="F68" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>1232</v>
+      </c>
+      <c r="H68" s="7" t="n">
+        <v>821</v>
+      </c>
+      <c r="I68" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="G68" s="7" t="n">
-        <v>821</v>
-      </c>
-      <c r="H68" s="7" t="n">
+      <c r="J68" s="7" t="n">
         <v>545</v>
       </c>
-      <c r="I68" s="7" t="n">
+      <c r="K68" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="J68" s="7" t="n">
+      <c r="L68" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="K68" s="7" t="n">
+      <c r="M68" s="7" t="n">
         <v>123</v>
       </c>
-      <c r="L68" s="7" t="n">
+      <c r="N68" s="7" t="n">
         <v>165</v>
       </c>
-      <c r="M68" s="6" t="n">
+      <c r="O68" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="N68" s="7" t="n">
+      <c r="P68" s="7" t="n">
         <v>36539</v>
+      </c>
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -3076,31 +3633,42 @@
         <v>1076</v>
       </c>
       <c r="F69" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="G69" s="7" t="n">
+        <v>1076</v>
+      </c>
+      <c r="H69" s="7" t="n">
+        <v>717</v>
+      </c>
+      <c r="I69" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="G69" s="7" t="n">
-        <v>717</v>
-      </c>
-      <c r="H69" s="7" t="n">
+      <c r="J69" s="7" t="n">
         <v>483</v>
       </c>
-      <c r="I69" s="7" t="n">
+      <c r="K69" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="J69" s="7" t="n">
+      <c r="L69" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="K69" s="7" t="n">
+      <c r="M69" s="7" t="n">
         <v>108</v>
       </c>
-      <c r="L69" s="7" t="n">
+      <c r="N69" s="7" t="n">
         <v>94</v>
       </c>
-      <c r="M69" s="6" t="n">
+      <c r="O69" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="N69" s="7" t="n">
+      <c r="P69" s="7" t="n">
         <v>18953</v>
+      </c>
+      <c r="Q69" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -3125,9 +3693,12 @@
       <c r="K70" s="9" t="n"/>
       <c r="L70" s="9" t="n"/>
       <c r="M70" s="9" t="n"/>
-      <c r="N70" s="10" t="n">
+      <c r="N70" s="9" t="n"/>
+      <c r="O70" s="9" t="n"/>
+      <c r="P70" s="10" t="n">
         <v>365786</v>
       </c>
+      <c r="Q70" s="9" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -3148,6 +3719,9 @@
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="5" t="n"/>
       <c r="N71" s="5" t="n"/>
+      <c r="O71" s="5" t="n"/>
+      <c r="P71" s="5" t="n"/>
+      <c r="Q71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -3168,31 +3742,42 @@
         <v>1699</v>
       </c>
       <c r="F72" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>1699</v>
+      </c>
+      <c r="H72" s="7" t="n">
+        <v>1133</v>
+      </c>
+      <c r="I72" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G72" s="7" t="n">
-        <v>1133</v>
-      </c>
-      <c r="H72" s="7" t="n">
+      <c r="J72" s="7" t="n">
         <v>706</v>
       </c>
-      <c r="I72" s="7" t="n">
+      <c r="K72" s="7" t="n">
         <v>84</v>
       </c>
-      <c r="J72" s="7" t="n">
+      <c r="L72" s="7" t="n">
         <v>101</v>
       </c>
-      <c r="K72" s="7" t="n">
+      <c r="M72" s="7" t="n">
         <v>170</v>
       </c>
-      <c r="L72" s="7" t="n">
+      <c r="N72" s="7" t="n">
         <v>175</v>
       </c>
-      <c r="M72" s="6" t="n">
+      <c r="O72" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="N72" s="7" t="n">
+      <c r="P72" s="7" t="n">
         <v>171348</v>
+      </c>
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -3217,9 +3802,12 @@
       <c r="K73" s="9" t="n"/>
       <c r="L73" s="9" t="n"/>
       <c r="M73" s="9" t="n"/>
-      <c r="N73" s="10" t="n">
+      <c r="N73" s="9" t="n"/>
+      <c r="O73" s="9" t="n"/>
+      <c r="P73" s="10" t="n">
         <v>171348</v>
       </c>
+      <c r="Q73" s="9" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -3240,6 +3828,9 @@
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="5" t="n"/>
       <c r="N74" s="5" t="n"/>
+      <c r="O74" s="5" t="n"/>
+      <c r="P74" s="5" t="n"/>
+      <c r="Q74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -3260,31 +3851,42 @@
         <v>2010</v>
       </c>
       <c r="F75" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H75" s="7" t="n">
+        <v>1341</v>
+      </c>
+      <c r="I75" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G75" s="7" t="n">
-        <v>1341</v>
-      </c>
-      <c r="H75" s="7" t="n">
+      <c r="J75" s="7" t="n">
         <v>832</v>
       </c>
-      <c r="I75" s="7" t="n">
+      <c r="K75" s="7" t="n">
         <v>84</v>
       </c>
-      <c r="J75" s="7" t="n">
+      <c r="L75" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="K75" s="7" t="n">
+      <c r="M75" s="7" t="n">
         <v>201</v>
       </c>
-      <c r="L75" s="7" t="n">
+      <c r="N75" s="7" t="n">
         <v>318</v>
       </c>
-      <c r="M75" s="6" t="n">
+      <c r="O75" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="N75" s="7" t="n">
+      <c r="P75" s="7" t="n">
         <v>264832</v>
+      </c>
+      <c r="Q75" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -3309,9 +3911,12 @@
       <c r="K76" s="9" t="n"/>
       <c r="L76" s="9" t="n"/>
       <c r="M76" s="9" t="n"/>
-      <c r="N76" s="10" t="n">
+      <c r="N76" s="9" t="n"/>
+      <c r="O76" s="9" t="n"/>
+      <c r="P76" s="10" t="n">
         <v>264832</v>
       </c>
+      <c r="Q76" s="9" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -3332,6 +3937,9 @@
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="5" t="n"/>
       <c r="N77" s="5" t="n"/>
+      <c r="O77" s="5" t="n"/>
+      <c r="P77" s="5" t="n"/>
+      <c r="Q77" s="5" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -3352,31 +3960,42 @@
         <v>765</v>
       </c>
       <c r="F78" s="6" t="n">
+        <v>143</v>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>765</v>
+      </c>
+      <c r="H78" s="7" t="n">
+        <v>510</v>
+      </c>
+      <c r="I78" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G78" s="7" t="n">
-        <v>510</v>
-      </c>
-      <c r="H78" s="7" t="n">
+      <c r="J78" s="7" t="n">
         <v>339</v>
       </c>
-      <c r="I78" s="7" t="n">
+      <c r="K78" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="J78" s="7" t="n">
+      <c r="L78" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="K78" s="7" t="n">
+      <c r="M78" s="7" t="n">
         <v>76</v>
       </c>
-      <c r="L78" s="7" t="n">
+      <c r="N78" s="7" t="n">
         <v>155</v>
       </c>
-      <c r="M78" s="6" t="n">
+      <c r="O78" s="6" t="n">
         <v>143</v>
       </c>
-      <c r="N78" s="7" t="n">
+      <c r="P78" s="7" t="n">
         <v>54752</v>
+      </c>
+      <c r="Q78" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -3401,9 +4020,12 @@
       <c r="K79" s="9" t="n"/>
       <c r="L79" s="9" t="n"/>
       <c r="M79" s="9" t="n"/>
-      <c r="N79" s="10" t="n">
+      <c r="N79" s="9" t="n"/>
+      <c r="O79" s="9" t="n"/>
+      <c r="P79" s="10" t="n">
         <v>54752</v>
       </c>
+      <c r="Q79" s="9" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -3424,6 +4046,9 @@
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="5" t="n"/>
       <c r="N80" s="5" t="n"/>
+      <c r="O80" s="5" t="n"/>
+      <c r="P80" s="5" t="n"/>
+      <c r="Q80" s="5" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -3444,31 +4069,42 @@
         <v>764</v>
       </c>
       <c r="F81" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="G81" s="7" t="n">
+        <v>764</v>
+      </c>
+      <c r="H81" s="7" t="n">
+        <v>509</v>
+      </c>
+      <c r="I81" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="G81" s="7" t="n">
-        <v>509</v>
-      </c>
-      <c r="H81" s="7" t="n">
+      <c r="J81" s="7" t="n">
         <v>307</v>
       </c>
-      <c r="I81" s="7" t="n">
+      <c r="K81" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="J81" s="7" t="n">
+      <c r="L81" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="K81" s="7" t="n">
+      <c r="M81" s="7" t="n">
         <v>76</v>
       </c>
-      <c r="L81" s="7" t="n">
+      <c r="N81" s="7" t="n">
         <v>139</v>
       </c>
-      <c r="M81" s="6" t="n">
+      <c r="O81" s="6" t="n">
         <v>106</v>
       </c>
-      <c r="N81" s="7" t="n">
+      <c r="P81" s="7" t="n">
         <v>31307</v>
+      </c>
+      <c r="Q81" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -3493,9 +4129,12 @@
       <c r="K82" s="9" t="n"/>
       <c r="L82" s="9" t="n"/>
       <c r="M82" s="9" t="n"/>
-      <c r="N82" s="10" t="n">
+      <c r="N82" s="9" t="n"/>
+      <c r="O82" s="9" t="n"/>
+      <c r="P82" s="10" t="n">
         <v>31307</v>
       </c>
+      <c r="Q82" s="9" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -3516,6 +4155,9 @@
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="5" t="n"/>
       <c r="N83" s="5" t="n"/>
+      <c r="O83" s="5" t="n"/>
+      <c r="P83" s="5" t="n"/>
+      <c r="Q83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -3536,31 +4178,42 @@
         <v>4191</v>
       </c>
       <c r="F84" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="G84" s="7" t="n">
+        <v>4191</v>
+      </c>
+      <c r="H84" s="7" t="n">
+        <v>2795</v>
+      </c>
+      <c r="I84" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G84" s="7" t="n">
-        <v>2795</v>
-      </c>
-      <c r="H84" s="7" t="n">
+      <c r="J84" s="7" t="n">
         <v>1851</v>
       </c>
-      <c r="I84" s="7" t="n">
+      <c r="K84" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="J84" s="7" t="n">
+      <c r="L84" s="7" t="n">
         <v>218</v>
       </c>
-      <c r="K84" s="7" t="n">
+      <c r="M84" s="7" t="n">
         <v>419</v>
       </c>
-      <c r="L84" s="7" t="n">
+      <c r="N84" s="7" t="n">
         <v>759</v>
       </c>
-      <c r="M84" s="6" t="n">
+      <c r="O84" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="N84" s="7" t="n">
+      <c r="P84" s="7" t="n">
         <v>945494</v>
+      </c>
+      <c r="Q84" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -3582,77 +4235,99 @@
         <v>2789</v>
       </c>
       <c r="F85" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="G85" s="7" t="n">
+        <v>2789</v>
+      </c>
+      <c r="H85" s="7" t="n">
+        <v>1860</v>
+      </c>
+      <c r="I85" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G85" s="7" t="n">
-        <v>1860</v>
-      </c>
-      <c r="H85" s="7" t="n">
+      <c r="J85" s="7" t="n">
         <v>1232</v>
       </c>
-      <c r="I85" s="7" t="n">
+      <c r="K85" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="J85" s="7" t="n">
+      <c r="L85" s="7" t="n">
         <v>148</v>
       </c>
-      <c r="K85" s="7" t="n">
+      <c r="M85" s="7" t="n">
         <v>279</v>
       </c>
-      <c r="L85" s="7" t="n">
+      <c r="N85" s="7" t="n">
         <v>444</v>
       </c>
-      <c r="M85" s="6" t="n">
+      <c r="O85" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="N85" s="7" t="n">
+      <c r="P85" s="7" t="n">
         <v>283826</v>
       </c>
+      <c r="Q85" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="inlineStr">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
         </is>
       </c>
-      <c r="B86" s="6" t="n">
+      <c r="B86" s="11" t="n">
         <v>198143251</v>
       </c>
-      <c r="C86" s="7" t="n">
+      <c r="C86" s="12" t="n">
         <v>735.34</v>
       </c>
-      <c r="D86" s="6" t="n">
+      <c r="D86" s="11" t="n">
         <v>490</v>
       </c>
-      <c r="E86" s="7" t="n">
+      <c r="E86" s="12" t="n">
+        <v>2166</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G86" s="12" t="n">
         <v>2499</v>
       </c>
-      <c r="F86" s="6" t="n">
+      <c r="H86" s="12" t="n">
+        <v>1667</v>
+      </c>
+      <c r="I86" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G86" s="7" t="n">
-        <v>1667</v>
-      </c>
-      <c r="H86" s="7" t="n">
+      <c r="J86" s="12" t="n">
         <v>1103</v>
       </c>
-      <c r="I86" s="7" t="n">
+      <c r="K86" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="J86" s="7" t="n">
+      <c r="L86" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="K86" s="7" t="n">
+      <c r="M86" s="12" t="n">
         <v>250</v>
       </c>
-      <c r="L86" s="7" t="n">
+      <c r="N86" s="12" t="n">
         <v>221</v>
       </c>
-      <c r="M86" s="6" t="n">
+      <c r="O86" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N86" s="7" t="n">
+      <c r="P86" s="12" t="n">
         <v>108095</v>
+      </c>
+      <c r="Q86" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -3674,31 +4349,42 @@
         <v>3723</v>
       </c>
       <c r="F87" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="G87" s="7" t="n">
+        <v>3723</v>
+      </c>
+      <c r="H87" s="7" t="n">
+        <v>2483</v>
+      </c>
+      <c r="I87" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G87" s="7" t="n">
-        <v>2483</v>
-      </c>
-      <c r="H87" s="7" t="n">
+      <c r="J87" s="7" t="n">
         <v>1649</v>
       </c>
-      <c r="I87" s="7" t="n">
+      <c r="K87" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="J87" s="7" t="n">
+      <c r="L87" s="7" t="n">
         <v>194</v>
       </c>
-      <c r="K87" s="7" t="n">
+      <c r="M87" s="7" t="n">
         <v>372</v>
       </c>
-      <c r="L87" s="7" t="n">
+      <c r="N87" s="7" t="n">
         <v>606</v>
       </c>
-      <c r="M87" s="6" t="n">
+      <c r="O87" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="N87" s="7" t="n">
+      <c r="P87" s="7" t="n">
         <v>91489</v>
+      </c>
+      <c r="Q87" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -3720,31 +4406,42 @@
         <v>3412</v>
       </c>
       <c r="F88" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="G88" s="7" t="n">
+        <v>3412</v>
+      </c>
+      <c r="H88" s="7" t="n">
+        <v>2276</v>
+      </c>
+      <c r="I88" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G88" s="7" t="n">
-        <v>2276</v>
-      </c>
-      <c r="H88" s="7" t="n">
+      <c r="J88" s="7" t="n">
         <v>1521</v>
       </c>
-      <c r="I88" s="7" t="n">
+      <c r="K88" s="7" t="n">
         <v>88</v>
       </c>
-      <c r="J88" s="7" t="n">
+      <c r="L88" s="7" t="n">
         <v>180</v>
       </c>
-      <c r="K88" s="7" t="n">
+      <c r="M88" s="7" t="n">
         <v>341</v>
       </c>
-      <c r="L88" s="7" t="n">
+      <c r="N88" s="7" t="n">
         <v>542</v>
       </c>
-      <c r="M88" s="6" t="n">
+      <c r="O88" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="N88" s="7" t="n">
+      <c r="P88" s="7" t="n">
         <v>258423</v>
+      </c>
+      <c r="Q88" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -3766,31 +4463,42 @@
         <v>4503</v>
       </c>
       <c r="F89" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="G89" s="7" t="n">
+        <v>4503</v>
+      </c>
+      <c r="H89" s="7" t="n">
+        <v>3004</v>
+      </c>
+      <c r="I89" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G89" s="7" t="n">
-        <v>3004</v>
-      </c>
-      <c r="H89" s="7" t="n">
+      <c r="J89" s="7" t="n">
         <v>1984</v>
       </c>
-      <c r="I89" s="7" t="n">
+      <c r="K89" s="7" t="n">
         <v>131</v>
       </c>
-      <c r="J89" s="7" t="n">
+      <c r="L89" s="7" t="n">
         <v>252</v>
       </c>
-      <c r="K89" s="7" t="n">
+      <c r="M89" s="7" t="n">
         <v>450</v>
       </c>
-      <c r="L89" s="7" t="n">
+      <c r="N89" s="7" t="n">
         <v>690</v>
       </c>
-      <c r="M89" s="6" t="n">
+      <c r="O89" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="N89" s="7" t="n">
+      <c r="P89" s="7" t="n">
         <v>415986</v>
+      </c>
+      <c r="Q89" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -3815,9 +4523,12 @@
       <c r="K90" s="9" t="n"/>
       <c r="L90" s="9" t="n"/>
       <c r="M90" s="9" t="n"/>
-      <c r="N90" s="10" t="n">
+      <c r="N90" s="9" t="n"/>
+      <c r="O90" s="9" t="n"/>
+      <c r="P90" s="10" t="n">
         <v>2103313</v>
       </c>
+      <c r="Q90" s="9" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -3838,51 +4549,65 @@
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="5" t="n"/>
       <c r="N91" s="5" t="n"/>
+      <c r="O91" s="5" t="n"/>
+      <c r="P91" s="5" t="n"/>
+      <c r="Q91" s="5" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t>MASIL - 8 Seconds Salon Hair Mask 350ml Set [350ml+8ml*2]</t>
         </is>
       </c>
-      <c r="B92" s="6" t="n">
+      <c r="B92" s="11" t="n">
         <v>183030830</v>
       </c>
-      <c r="C92" s="7" t="n">
+      <c r="C92" s="12" t="n">
         <v>669.05</v>
       </c>
-      <c r="D92" s="6" t="n">
+      <c r="D92" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="E92" s="7" t="n">
+      <c r="E92" s="12" t="n">
+        <v>2010</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G92" s="12" t="n">
         <v>2412</v>
       </c>
-      <c r="F92" s="6" t="n">
+      <c r="H92" s="12" t="n">
+        <v>1609</v>
+      </c>
+      <c r="I92" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G92" s="7" t="n">
-        <v>1609</v>
-      </c>
-      <c r="H92" s="7" t="n">
+      <c r="J92" s="12" t="n">
         <v>1051</v>
       </c>
-      <c r="I92" s="7" t="n">
+      <c r="K92" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="J92" s="7" t="n">
+      <c r="L92" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="K92" s="7" t="n">
+      <c r="M92" s="12" t="n">
         <v>241</v>
       </c>
-      <c r="L92" s="7" t="n">
+      <c r="N92" s="12" t="n">
         <v>201</v>
       </c>
-      <c r="M92" s="6" t="n">
+      <c r="O92" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N92" s="7" t="n">
+      <c r="P92" s="12" t="n">
         <v>21075</v>
+      </c>
+      <c r="Q92" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -3907,9 +4632,12 @@
       <c r="K93" s="9" t="n"/>
       <c r="L93" s="9" t="n"/>
       <c r="M93" s="9" t="n"/>
-      <c r="N93" s="10" t="n">
+      <c r="N93" s="9" t="n"/>
+      <c r="O93" s="9" t="n"/>
+      <c r="P93" s="10" t="n">
         <v>21075</v>
       </c>
+      <c r="Q93" s="9" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -3930,6 +4658,9 @@
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="5" t="n"/>
       <c r="N94" s="5" t="n"/>
+      <c r="O94" s="5" t="n"/>
+      <c r="P94" s="5" t="n"/>
+      <c r="Q94" s="5" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
@@ -3950,169 +4681,213 @@
         <v>1543</v>
       </c>
       <c r="F95" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="G95" s="7" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H95" s="7" t="n">
+        <v>1029</v>
+      </c>
+      <c r="I95" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G95" s="7" t="n">
-        <v>1029</v>
-      </c>
-      <c r="H95" s="7" t="n">
+      <c r="J95" s="7" t="n">
         <v>687</v>
       </c>
-      <c r="I95" s="7" t="n">
+      <c r="K95" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="J95" s="7" t="n">
+      <c r="L95" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="K95" s="7" t="n">
+      <c r="M95" s="7" t="n">
         <v>154</v>
       </c>
-      <c r="L95" s="7" t="n">
+      <c r="N95" s="7" t="n">
         <v>178</v>
       </c>
-      <c r="M95" s="6" t="n">
+      <c r="O95" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="N95" s="7" t="n">
+      <c r="P95" s="7" t="n">
         <v>114141</v>
       </c>
+      <c r="Q95" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="inlineStr">
+      <c r="A96" s="11" t="inlineStr">
         <is>
           <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
         </is>
       </c>
-      <c r="B96" s="6" t="n">
+      <c r="B96" s="11" t="n">
         <v>180988755</v>
       </c>
-      <c r="C96" s="7" t="n">
+      <c r="C96" s="12" t="n">
         <v>486.69</v>
       </c>
-      <c r="D96" s="6" t="n">
+      <c r="D96" s="11" t="n">
         <v>406</v>
       </c>
-      <c r="E96" s="7" t="n">
+      <c r="E96" s="12" t="n">
+        <v>1699</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="G96" s="12" t="n">
         <v>1745</v>
       </c>
-      <c r="F96" s="6" t="n">
+      <c r="H96" s="12" t="n">
+        <v>1164</v>
+      </c>
+      <c r="I96" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G96" s="7" t="n">
-        <v>1164</v>
-      </c>
-      <c r="H96" s="7" t="n">
+      <c r="J96" s="12" t="n">
         <v>775</v>
       </c>
-      <c r="I96" s="7" t="n">
+      <c r="K96" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="J96" s="7" t="n">
+      <c r="L96" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="K96" s="7" t="n">
+      <c r="M96" s="12" t="n">
         <v>174</v>
       </c>
-      <c r="L96" s="7" t="n">
+      <c r="N96" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="M96" s="6" t="n">
+      <c r="O96" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N96" s="7" t="n">
+      <c r="P96" s="12" t="n">
         <v>59279</v>
       </c>
+      <c r="Q96" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="6" t="inlineStr">
+      <c r="A97" s="11" t="inlineStr">
         <is>
           <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / Смягчающие гидрогелевые патчи для глаз с экстрактом артишока</t>
         </is>
       </c>
-      <c r="B97" s="6" t="n">
+      <c r="B97" s="11" t="n">
         <v>179611278</v>
       </c>
-      <c r="C97" s="7" t="n">
+      <c r="C97" s="12" t="n">
         <v>415.46</v>
       </c>
-      <c r="D97" s="6" t="n">
+      <c r="D97" s="11" t="n">
         <v>156</v>
       </c>
-      <c r="E97" s="7" t="n">
+      <c r="E97" s="12" t="n">
+        <v>1387</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="G97" s="12" t="n">
         <v>1485</v>
       </c>
-      <c r="F97" s="6" t="n">
+      <c r="H97" s="12" t="n">
+        <v>990</v>
+      </c>
+      <c r="I97" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G97" s="7" t="n">
-        <v>990</v>
-      </c>
-      <c r="H97" s="7" t="n">
+      <c r="J97" s="12" t="n">
         <v>656</v>
       </c>
-      <c r="I97" s="7" t="n">
+      <c r="K97" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="J97" s="7" t="n">
+      <c r="L97" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="K97" s="7" t="n">
+      <c r="M97" s="12" t="n">
         <v>148</v>
       </c>
-      <c r="L97" s="7" t="n">
+      <c r="N97" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="M97" s="6" t="n">
+      <c r="O97" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N97" s="7" t="n">
+      <c r="P97" s="12" t="n">
         <v>19444</v>
       </c>
+      <c r="Q97" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="6" t="inlineStr">
+      <c r="A98" s="11" t="inlineStr">
         <is>
           <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
         </is>
       </c>
-      <c r="B98" s="6" t="n">
+      <c r="B98" s="11" t="n">
         <v>180992464</v>
       </c>
-      <c r="C98" s="7" t="n">
+      <c r="C98" s="12" t="n">
         <v>591.29</v>
       </c>
-      <c r="D98" s="6" t="n">
+      <c r="D98" s="11" t="n">
         <v>89</v>
       </c>
-      <c r="E98" s="7" t="n">
+      <c r="E98" s="12" t="n">
+        <v>2010</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G98" s="12" t="n">
         <v>2090</v>
       </c>
-      <c r="F98" s="6" t="n">
+      <c r="H98" s="12" t="n">
+        <v>1394</v>
+      </c>
+      <c r="I98" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G98" s="7" t="n">
-        <v>1394</v>
-      </c>
-      <c r="H98" s="7" t="n">
+      <c r="J98" s="12" t="n">
         <v>945</v>
       </c>
-      <c r="I98" s="7" t="n">
+      <c r="K98" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="J98" s="7" t="n">
+      <c r="L98" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="K98" s="7" t="n">
+      <c r="M98" s="12" t="n">
         <v>209</v>
       </c>
-      <c r="L98" s="7" t="n">
+      <c r="N98" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="M98" s="6" t="n">
+      <c r="O98" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N98" s="7" t="n">
+      <c r="P98" s="12" t="n">
         <v>15787</v>
+      </c>
+      <c r="Q98" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -4134,215 +4909,270 @@
         <v>1543</v>
       </c>
       <c r="F99" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="G99" s="7" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H99" s="7" t="n">
+        <v>1029</v>
+      </c>
+      <c r="I99" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G99" s="7" t="n">
-        <v>1029</v>
-      </c>
-      <c r="H99" s="7" t="n">
+      <c r="J99" s="7" t="n">
         <v>684</v>
       </c>
-      <c r="I99" s="7" t="n">
+      <c r="K99" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="J99" s="7" t="n">
+      <c r="L99" s="7" t="n">
         <v>86</v>
       </c>
-      <c r="K99" s="7" t="n">
+      <c r="M99" s="7" t="n">
         <v>154</v>
       </c>
-      <c r="L99" s="7" t="n">
+      <c r="N99" s="7" t="n">
         <v>135</v>
       </c>
-      <c r="M99" s="6" t="n">
+      <c r="O99" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="N99" s="7" t="n">
+      <c r="P99" s="7" t="n">
         <v>19449</v>
       </c>
+      <c r="Q99" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="6" t="inlineStr">
+      <c r="A100" s="11" t="inlineStr">
         <is>
           <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
         </is>
       </c>
-      <c r="B100" s="6" t="n">
+      <c r="B100" s="11" t="n">
         <v>180987509</v>
       </c>
-      <c r="C100" s="7" t="n">
+      <c r="C100" s="12" t="n">
         <v>486.69</v>
       </c>
-      <c r="D100" s="6" t="n">
+      <c r="D100" s="11" t="n">
         <v>202</v>
       </c>
-      <c r="E100" s="7" t="n">
+      <c r="E100" s="12" t="n">
+        <v>1699</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="G100" s="12" t="n">
         <v>1718</v>
       </c>
-      <c r="F100" s="6" t="n">
+      <c r="H100" s="12" t="n">
+        <v>1146</v>
+      </c>
+      <c r="I100" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G100" s="7" t="n">
-        <v>1146</v>
-      </c>
-      <c r="H100" s="7" t="n">
+      <c r="J100" s="12" t="n">
         <v>763</v>
       </c>
-      <c r="I100" s="7" t="n">
+      <c r="K100" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="J100" s="7" t="n">
+      <c r="L100" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="K100" s="7" t="n">
+      <c r="M100" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="L100" s="7" t="n">
+      <c r="N100" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="M100" s="6" t="n">
+      <c r="O100" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N100" s="7" t="n">
+      <c r="P100" s="12" t="n">
         <v>29493</v>
       </c>
+      <c r="Q100" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="6" t="inlineStr">
+      <c r="A101" s="11" t="inlineStr">
         <is>
           <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с черным жемчугом и золотом</t>
         </is>
       </c>
-      <c r="B101" s="6" t="n">
+      <c r="B101" s="11" t="n">
         <v>151175880</v>
       </c>
-      <c r="C101" s="7" t="n">
+      <c r="C101" s="12" t="n">
         <v>387.67</v>
       </c>
-      <c r="D101" s="6" t="n">
+      <c r="D101" s="11" t="n">
         <v>549</v>
       </c>
-      <c r="E101" s="7" t="n">
+      <c r="E101" s="12" t="n">
+        <v>1387</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="G101" s="12" t="n">
         <v>1407</v>
       </c>
-      <c r="F101" s="6" t="n">
+      <c r="H101" s="12" t="n">
+        <v>939</v>
+      </c>
+      <c r="I101" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G101" s="7" t="n">
-        <v>939</v>
-      </c>
-      <c r="H101" s="7" t="n">
+      <c r="J101" s="12" t="n">
         <v>632</v>
       </c>
-      <c r="I101" s="7" t="n">
+      <c r="K101" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="J101" s="7" t="n">
+      <c r="L101" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="K101" s="7" t="n">
+      <c r="M101" s="12" t="n">
         <v>141</v>
       </c>
-      <c r="L101" s="7" t="n">
+      <c r="N101" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="M101" s="6" t="n">
+      <c r="O101" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N101" s="7" t="n">
+      <c r="P101" s="12" t="n">
         <v>63849</v>
       </c>
+      <c r="Q101" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="6" t="inlineStr">
+      <c r="A102" s="11" t="inlineStr">
         <is>
           <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлаждающие гидрогелевые патчи для глаз с экстрактом агавы</t>
         </is>
       </c>
-      <c r="B102" s="6" t="n">
+      <c r="B102" s="11" t="n">
         <v>151175877</v>
       </c>
-      <c r="C102" s="7" t="n">
+      <c r="C102" s="12" t="n">
         <v>415.46</v>
       </c>
-      <c r="D102" s="6" t="n">
+      <c r="D102" s="11" t="n">
         <v>501</v>
       </c>
-      <c r="E102" s="7" t="n">
+      <c r="E102" s="12" t="n">
+        <v>1387</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="G102" s="12" t="n">
         <v>1488</v>
       </c>
-      <c r="F102" s="6" t="n">
+      <c r="H102" s="12" t="n">
+        <v>993</v>
+      </c>
+      <c r="I102" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G102" s="7" t="n">
-        <v>993</v>
-      </c>
-      <c r="H102" s="7" t="n">
+      <c r="J102" s="12" t="n">
         <v>661</v>
       </c>
-      <c r="I102" s="7" t="n">
+      <c r="K102" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="J102" s="7" t="n">
+      <c r="L102" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="K102" s="7" t="n">
+      <c r="M102" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="L102" s="7" t="n">
+      <c r="N102" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="M102" s="6" t="n">
+      <c r="O102" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N102" s="7" t="n">
+      <c r="P102" s="12" t="n">
         <v>62444</v>
       </c>
+      <c r="Q102" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="6" t="inlineStr">
+      <c r="A103" s="11" t="inlineStr">
         <is>
           <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
         </is>
       </c>
-      <c r="B103" s="6" t="n">
+      <c r="B103" s="11" t="n">
         <v>179611207</v>
       </c>
-      <c r="C103" s="7" t="n">
+      <c r="C103" s="12" t="n">
         <v>415.46</v>
       </c>
-      <c r="D103" s="6" t="n">
+      <c r="D103" s="11" t="n">
         <v>608</v>
       </c>
-      <c r="E103" s="7" t="n">
+      <c r="E103" s="12" t="n">
+        <v>1232</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G103" s="12" t="n">
         <v>1488</v>
       </c>
-      <c r="F103" s="6" t="n">
+      <c r="H103" s="12" t="n">
+        <v>991</v>
+      </c>
+      <c r="I103" s="11" t="n">
         <v>33.4</v>
       </c>
-      <c r="G103" s="7" t="n">
-        <v>991</v>
-      </c>
-      <c r="H103" s="7" t="n">
+      <c r="J103" s="12" t="n">
         <v>658</v>
       </c>
-      <c r="I103" s="7" t="n">
+      <c r="K103" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="J103" s="7" t="n">
+      <c r="L103" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="K103" s="7" t="n">
+      <c r="M103" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="L103" s="7" t="n">
+      <c r="N103" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="M103" s="6" t="n">
+      <c r="O103" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N103" s="7" t="n">
+      <c r="P103" s="12" t="n">
         <v>75780</v>
+      </c>
+      <c r="Q103" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -4364,119 +5194,144 @@
         <v>1543</v>
       </c>
       <c r="F104" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="G104" s="7" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H104" s="7" t="n">
+        <v>1029</v>
+      </c>
+      <c r="I104" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G104" s="7" t="n">
-        <v>1029</v>
-      </c>
-      <c r="H104" s="7" t="n">
+      <c r="J104" s="7" t="n">
         <v>684</v>
       </c>
-      <c r="I104" s="7" t="n">
+      <c r="K104" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="J104" s="7" t="n">
+      <c r="L104" s="7" t="n">
         <v>87</v>
       </c>
-      <c r="K104" s="7" t="n">
+      <c r="M104" s="7" t="n">
         <v>154</v>
       </c>
-      <c r="L104" s="7" t="n">
+      <c r="N104" s="7" t="n">
         <v>151</v>
       </c>
-      <c r="M104" s="6" t="n">
+      <c r="O104" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="N104" s="7" t="n">
+      <c r="P104" s="7" t="n">
         <v>61249</v>
       </c>
+      <c r="Q104" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="6" t="inlineStr">
+      <c r="A105" s="11" t="inlineStr">
         <is>
           <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]/ Гидрогелевые патчи для глаз с черным жемчугом и золотом 1 пара</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr"/>
-      <c r="C105" s="7" t="n">
+      <c r="B105" s="11" t="inlineStr"/>
+      <c r="C105" s="12" t="n">
         <v>71.23999999999999</v>
       </c>
-      <c r="D105" s="6" t="n">
+      <c r="D105" s="11" t="n">
         <v>320</v>
       </c>
-      <c r="E105" s="7" t="n">
+      <c r="E105" s="12" t="n"/>
+      <c r="F105" s="11" t="n"/>
+      <c r="G105" s="12" t="n">
         <v>391</v>
       </c>
-      <c r="F105" s="6" t="n">
+      <c r="H105" s="12" t="n">
+        <v>262</v>
+      </c>
+      <c r="I105" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="G105" s="7" t="n">
+      <c r="J105" s="12" t="n">
+        <v>172</v>
+      </c>
+      <c r="K105" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="L105" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="M105" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="N105" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="O105" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="P105" s="12" t="n">
+        <v>9147</v>
+      </c>
+      <c r="Q105" s="11" t="inlineStr">
+        <is>
+          <t>Поднять до ROI30 (нет цены)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs] / гидрогелевые патчи для глаз с золотом 1 пара</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr"/>
+      <c r="C106" s="12" t="n">
+        <v>71.23999999999999</v>
+      </c>
+      <c r="D106" s="11" t="n">
+        <v>428</v>
+      </c>
+      <c r="E106" s="12" t="n"/>
+      <c r="F106" s="11" t="n"/>
+      <c r="G106" s="12" t="n">
+        <v>391</v>
+      </c>
+      <c r="H106" s="12" t="n">
         <v>262</v>
       </c>
-      <c r="H105" s="7" t="n">
+      <c r="I106" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="J106" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="I105" s="7" t="n">
+      <c r="K106" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="J105" s="7" t="n">
+      <c r="L106" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="K105" s="7" t="n">
+      <c r="M106" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="L105" s="7" t="n">
+      <c r="N106" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="M105" s="6" t="n">
+      <c r="O106" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N105" s="7" t="n">
+      <c r="P106" s="12" t="n">
         <v>9147</v>
       </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs] / гидрогелевые патчи для глаз с золотом 1 пара</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr"/>
-      <c r="C106" s="7" t="n">
-        <v>71.23999999999999</v>
-      </c>
-      <c r="D106" s="6" t="n">
-        <v>428</v>
-      </c>
-      <c r="E106" s="7" t="n">
-        <v>391</v>
-      </c>
-      <c r="F106" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="G106" s="7" t="n">
-        <v>262</v>
-      </c>
-      <c r="H106" s="7" t="n">
-        <v>172</v>
-      </c>
-      <c r="I106" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="J106" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="K106" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="L106" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="M106" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="N106" s="7" t="n">
-        <v>9147</v>
+      <c r="Q106" s="11" t="inlineStr">
+        <is>
+          <t>Поднять до ROI30 (нет цены)</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -4501,9 +5356,12 @@
       <c r="K107" s="9" t="n"/>
       <c r="L107" s="9" t="n"/>
       <c r="M107" s="9" t="n"/>
-      <c r="N107" s="10" t="n">
+      <c r="N107" s="9" t="n"/>
+      <c r="O107" s="9" t="n"/>
+      <c r="P107" s="10" t="n">
         <v>539209</v>
       </c>
+      <c r="Q107" s="9" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -4524,143 +5382,179 @@
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="5" t="n"/>
       <c r="N108" s="5" t="n"/>
+      <c r="O108" s="5" t="n"/>
+      <c r="P108" s="5" t="n"/>
+      <c r="Q108" s="5" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="6" t="inlineStr">
+      <c r="A109" s="11" t="inlineStr">
         <is>
           <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Охлаждающая гидрогелевая маска для лица с экстрактом агавы</t>
         </is>
       </c>
-      <c r="B109" s="6" t="n">
+      <c r="B109" s="11" t="n">
         <v>226115324</v>
       </c>
-      <c r="C109" s="7" t="n">
+      <c r="C109" s="12" t="n">
         <v>486.41</v>
       </c>
-      <c r="D109" s="6" t="n">
+      <c r="D109" s="11" t="n">
         <v>741</v>
       </c>
-      <c r="E109" s="7" t="n">
+      <c r="E109" s="12" t="n">
+        <v>1543</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G109" s="12" t="n">
         <v>1788</v>
       </c>
-      <c r="F109" s="6" t="n">
+      <c r="H109" s="12" t="n">
+        <v>1193</v>
+      </c>
+      <c r="I109" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G109" s="7" t="n">
-        <v>1193</v>
-      </c>
-      <c r="H109" s="7" t="n">
+      <c r="J109" s="12" t="n">
         <v>790</v>
       </c>
-      <c r="I109" s="7" t="n">
+      <c r="K109" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="J109" s="7" t="n">
+      <c r="L109" s="12" t="n">
         <v>107</v>
       </c>
-      <c r="K109" s="7" t="n">
+      <c r="M109" s="12" t="n">
         <v>179</v>
       </c>
-      <c r="L109" s="7" t="n">
+      <c r="N109" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="M109" s="6" t="n">
+      <c r="O109" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N109" s="7" t="n">
+      <c r="P109" s="12" t="n">
         <v>108129</v>
       </c>
+      <c r="Q109" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="6" t="inlineStr">
+      <c r="A110" s="11" t="inlineStr">
         <is>
           <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
         </is>
       </c>
-      <c r="B110" s="6" t="n">
+      <c r="B110" s="11" t="n">
         <v>226114935</v>
       </c>
-      <c r="C110" s="7" t="n">
+      <c r="C110" s="12" t="n">
         <v>507.16</v>
       </c>
-      <c r="D110" s="6" t="n">
+      <c r="D110" s="11" t="n">
         <v>529</v>
       </c>
-      <c r="E110" s="7" t="n">
+      <c r="E110" s="12" t="n">
+        <v>1698</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="G110" s="12" t="n">
         <v>1802</v>
       </c>
-      <c r="F110" s="6" t="n">
+      <c r="H110" s="12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="I110" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G110" s="7" t="n">
-        <v>1202</v>
-      </c>
-      <c r="H110" s="7" t="n">
+      <c r="J110" s="12" t="n">
         <v>796</v>
       </c>
-      <c r="I110" s="7" t="n">
+      <c r="K110" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="J110" s="7" t="n">
+      <c r="L110" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="K110" s="7" t="n">
+      <c r="M110" s="12" t="n">
         <v>180</v>
       </c>
-      <c r="L110" s="7" t="n">
+      <c r="N110" s="12" t="n">
         <v>152</v>
       </c>
-      <c r="M110" s="6" t="n">
+      <c r="O110" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N110" s="7" t="n">
+      <c r="P110" s="12" t="n">
         <v>80486</v>
       </c>
+      <c r="Q110" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="6" t="inlineStr">
+      <c r="A111" s="11" t="inlineStr">
         <is>
           <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тонизирующая гидрогелевая маска для лица с экстрактом какао</t>
         </is>
       </c>
-      <c r="B111" s="6" t="n">
+      <c r="B111" s="11" t="n">
         <v>226115248</v>
       </c>
-      <c r="C111" s="7" t="n">
+      <c r="C111" s="12" t="n">
         <v>496.86</v>
       </c>
-      <c r="D111" s="6" t="n">
+      <c r="D111" s="11" t="n">
         <v>399</v>
       </c>
-      <c r="E111" s="7" t="n">
+      <c r="E111" s="12" t="n">
+        <v>1543</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="G111" s="12" t="n">
         <v>1738</v>
       </c>
-      <c r="F111" s="6" t="n">
+      <c r="H111" s="12" t="n">
+        <v>1159</v>
+      </c>
+      <c r="I111" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G111" s="7" t="n">
-        <v>1159</v>
-      </c>
-      <c r="H111" s="7" t="n">
+      <c r="J111" s="12" t="n">
         <v>766</v>
       </c>
-      <c r="I111" s="7" t="n">
+      <c r="K111" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="J111" s="7" t="n">
+      <c r="L111" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="K111" s="7" t="n">
+      <c r="M111" s="12" t="n">
         <v>174</v>
       </c>
-      <c r="L111" s="7" t="n">
+      <c r="N111" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="M111" s="6" t="n">
+      <c r="O111" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N111" s="7" t="n">
+      <c r="P111" s="12" t="n">
         <v>59474</v>
+      </c>
+      <c r="Q111" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -4682,215 +5576,270 @@
         <v>2010</v>
       </c>
       <c r="F112" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G112" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H112" s="7" t="n">
+        <v>1341</v>
+      </c>
+      <c r="I112" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G112" s="7" t="n">
-        <v>1341</v>
-      </c>
-      <c r="H112" s="7" t="n">
+      <c r="J112" s="7" t="n">
         <v>893</v>
       </c>
-      <c r="I112" s="7" t="n">
+      <c r="K112" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="J112" s="7" t="n">
+      <c r="L112" s="7" t="n">
         <v>121</v>
       </c>
-      <c r="K112" s="7" t="n">
+      <c r="M112" s="7" t="n">
         <v>201</v>
       </c>
-      <c r="L112" s="7" t="n">
+      <c r="N112" s="7" t="n">
         <v>243</v>
       </c>
-      <c r="M112" s="6" t="n">
+      <c r="O112" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="N112" s="7" t="n">
+      <c r="P112" s="7" t="n">
         <v>79336</v>
       </c>
+      <c r="Q112" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="6" t="inlineStr">
+      <c r="A113" s="11" t="inlineStr">
         <is>
           <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом и экстрактом улитки</t>
         </is>
       </c>
-      <c r="B113" s="6" t="n">
+      <c r="B113" s="11" t="n">
         <v>226115141</v>
       </c>
-      <c r="C113" s="7" t="n">
+      <c r="C113" s="12" t="n">
         <v>478.17</v>
       </c>
-      <c r="D113" s="6" t="n">
+      <c r="D113" s="11" t="n">
         <v>273</v>
       </c>
-      <c r="E113" s="7" t="n">
+      <c r="E113" s="12" t="n">
+        <v>1699</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="G113" s="12" t="n">
         <v>1720</v>
       </c>
-      <c r="F113" s="6" t="n">
+      <c r="H113" s="12" t="n">
+        <v>1148</v>
+      </c>
+      <c r="I113" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G113" s="7" t="n">
-        <v>1148</v>
-      </c>
-      <c r="H113" s="7" t="n">
+      <c r="J113" s="12" t="n">
         <v>764</v>
       </c>
-      <c r="I113" s="7" t="n">
+      <c r="K113" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="J113" s="7" t="n">
+      <c r="L113" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="K113" s="7" t="n">
+      <c r="M113" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="L113" s="7" t="n">
+      <c r="N113" s="12" t="n">
         <v>143</v>
       </c>
-      <c r="M113" s="6" t="n">
+      <c r="O113" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N113" s="7" t="n">
+      <c r="P113" s="12" t="n">
         <v>39162</v>
       </c>
+      <c r="Q113" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="6" t="inlineStr">
+      <c r="A114" s="11" t="inlineStr">
         <is>
           <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с черным жемчугом и золотом</t>
         </is>
       </c>
-      <c r="B114" s="6" t="n">
+      <c r="B114" s="11" t="n">
         <v>226115478</v>
       </c>
-      <c r="C114" s="7" t="n">
+      <c r="C114" s="12" t="n">
         <v>478.05</v>
       </c>
-      <c r="D114" s="6" t="n">
+      <c r="D114" s="11" t="n">
         <v>292</v>
       </c>
-      <c r="E114" s="7" t="n">
+      <c r="E114" s="12" t="n">
+        <v>1543</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="G114" s="12" t="n">
         <v>1696</v>
       </c>
-      <c r="F114" s="6" t="n">
+      <c r="H114" s="12" t="n">
+        <v>1130</v>
+      </c>
+      <c r="I114" s="11" t="n">
         <v>33.4</v>
       </c>
-      <c r="G114" s="7" t="n">
-        <v>1130</v>
-      </c>
-      <c r="H114" s="7" t="n">
+      <c r="J114" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="I114" s="7" t="n">
+      <c r="K114" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="J114" s="7" t="n">
+      <c r="L114" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="K114" s="7" t="n">
+      <c r="M114" s="12" t="n">
         <v>170</v>
       </c>
-      <c r="L114" s="7" t="n">
+      <c r="N114" s="12" t="n">
         <v>143</v>
       </c>
-      <c r="M114" s="6" t="n">
+      <c r="O114" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N114" s="7" t="n">
+      <c r="P114" s="12" t="n">
         <v>41877</v>
       </c>
+      <c r="Q114" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="6" t="inlineStr">
+      <c r="A115" s="11" t="inlineStr">
         <is>
           <t>PETITFEE - MASK 5 (блек, агава, какао, артишок, голд снейл)</t>
         </is>
       </c>
-      <c r="B115" s="6" t="n">
+      <c r="B115" s="11" t="n">
         <v>1177994944</v>
       </c>
-      <c r="C115" s="7" t="n">
+      <c r="C115" s="12" t="n">
         <v>488</v>
       </c>
-      <c r="D115" s="6" t="n">
+      <c r="D115" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="E115" s="7" t="n">
+      <c r="E115" s="12" t="n">
+        <v>1499</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G115" s="12" t="n">
         <v>1747</v>
       </c>
-      <c r="F115" s="6" t="n">
+      <c r="H115" s="12" t="n">
+        <v>1164</v>
+      </c>
+      <c r="I115" s="11" t="n">
         <v>33.4</v>
       </c>
-      <c r="G115" s="7" t="n">
-        <v>1164</v>
-      </c>
-      <c r="H115" s="7" t="n">
+      <c r="J115" s="12" t="n">
         <v>760</v>
       </c>
-      <c r="I115" s="7" t="n">
+      <c r="K115" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="J115" s="7" t="n">
+      <c r="L115" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="K115" s="7" t="n">
+      <c r="M115" s="12" t="n">
         <v>175</v>
       </c>
-      <c r="L115" s="7" t="n">
+      <c r="N115" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="M115" s="6" t="n">
+      <c r="O115" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N115" s="7" t="n">
+      <c r="P115" s="12" t="n">
         <v>14640</v>
       </c>
+      <c r="Q115" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" s="6" t="inlineStr">
+      <c r="A116" s="11" t="inlineStr">
         <is>
           <t>PETITFEE - MASK 6 (блек, агава, какао, артишок, голд, ромашка)</t>
         </is>
       </c>
-      <c r="B116" s="6" t="n">
+      <c r="B116" s="11" t="n">
         <v>1175175447</v>
       </c>
-      <c r="C116" s="7" t="n">
+      <c r="C116" s="12" t="n">
         <v>593</v>
       </c>
-      <c r="D116" s="6" t="n">
+      <c r="D116" s="11" t="n">
         <v>106</v>
       </c>
-      <c r="E116" s="7" t="n">
+      <c r="E116" s="12" t="n">
+        <v>1511</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>-9</v>
+      </c>
+      <c r="G116" s="12" t="n">
         <v>2064</v>
       </c>
-      <c r="F116" s="6" t="n">
+      <c r="H116" s="12" t="n">
+        <v>1376</v>
+      </c>
+      <c r="I116" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G116" s="7" t="n">
-        <v>1376</v>
-      </c>
-      <c r="H116" s="7" t="n">
+      <c r="J116" s="12" t="n">
         <v>894</v>
       </c>
-      <c r="I116" s="7" t="n">
+      <c r="K116" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="J116" s="7" t="n">
+      <c r="L116" s="12" t="n">
         <v>111</v>
       </c>
-      <c r="K116" s="7" t="n">
+      <c r="M116" s="12" t="n">
         <v>206</v>
       </c>
-      <c r="L116" s="7" t="n">
+      <c r="N116" s="12" t="n">
         <v>178</v>
       </c>
-      <c r="M116" s="6" t="n">
+      <c r="O116" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N116" s="7" t="n">
+      <c r="P116" s="12" t="n">
         <v>18857</v>
+      </c>
+      <c r="Q116" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -4915,9 +5864,12 @@
       <c r="K117" s="9" t="n"/>
       <c r="L117" s="9" t="n"/>
       <c r="M117" s="9" t="n"/>
-      <c r="N117" s="10" t="n">
+      <c r="N117" s="9" t="n"/>
+      <c r="O117" s="9" t="n"/>
+      <c r="P117" s="10" t="n">
         <v>441961</v>
       </c>
+      <c r="Q117" s="9" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -4938,97 +5890,122 @@
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="5" t="n"/>
       <c r="N118" s="5" t="n"/>
+      <c r="O118" s="5" t="n"/>
+      <c r="P118" s="5" t="n"/>
+      <c r="Q118" s="5" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="6" t="inlineStr">
+      <c r="A119" s="11" t="inlineStr">
         <is>
           <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
         </is>
       </c>
-      <c r="B119" s="6" t="n">
+      <c r="B119" s="11" t="n">
         <v>437154709</v>
       </c>
-      <c r="C119" s="7" t="n">
+      <c r="C119" s="12" t="n">
         <v>463.19</v>
       </c>
-      <c r="D119" s="6" t="n">
+      <c r="D119" s="11" t="n">
         <v>5499</v>
       </c>
-      <c r="E119" s="7" t="n">
+      <c r="E119" s="12" t="n">
+        <v>1699</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="G119" s="12" t="n">
         <v>1767</v>
       </c>
-      <c r="F119" s="6" t="n">
+      <c r="H119" s="12" t="n">
+        <v>1178</v>
+      </c>
+      <c r="I119" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G119" s="7" t="n">
-        <v>1178</v>
-      </c>
-      <c r="H119" s="7" t="n">
+      <c r="J119" s="12" t="n">
         <v>783</v>
       </c>
-      <c r="I119" s="7" t="n">
+      <c r="K119" s="12" t="n">
         <v>110</v>
       </c>
-      <c r="J119" s="7" t="n">
+      <c r="L119" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="K119" s="7" t="n">
+      <c r="M119" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="L119" s="7" t="n">
+      <c r="N119" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="M119" s="6" t="n">
+      <c r="O119" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N119" s="7" t="n">
+      <c r="P119" s="12" t="n">
         <v>764125</v>
       </c>
+      <c r="Q119" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="6" t="inlineStr">
+      <c r="A120" s="11" t="inlineStr">
         <is>
           <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
         </is>
       </c>
-      <c r="B120" s="6" t="n">
+      <c r="B120" s="11" t="n">
         <v>437190353</v>
       </c>
-      <c r="C120" s="7" t="n">
+      <c r="C120" s="12" t="n">
         <v>1092.96</v>
       </c>
-      <c r="D120" s="6" t="n">
+      <c r="D120" s="11" t="n">
         <v>102</v>
       </c>
-      <c r="E120" s="7" t="n">
+      <c r="E120" s="12" t="n">
+        <v>2946</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G120" s="12" t="n">
         <v>3702</v>
       </c>
-      <c r="F120" s="6" t="n">
+      <c r="H120" s="12" t="n">
+        <v>2469</v>
+      </c>
+      <c r="I120" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G120" s="7" t="n">
-        <v>2469</v>
-      </c>
-      <c r="H120" s="7" t="n">
+      <c r="J120" s="12" t="n">
         <v>1642</v>
       </c>
-      <c r="I120" s="7" t="n">
+      <c r="K120" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="J120" s="7" t="n">
+      <c r="L120" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="K120" s="7" t="n">
+      <c r="M120" s="12" t="n">
         <v>370</v>
       </c>
-      <c r="L120" s="7" t="n">
+      <c r="N120" s="12" t="n">
         <v>328</v>
       </c>
-      <c r="M120" s="6" t="n">
+      <c r="O120" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N120" s="7" t="n">
+      <c r="P120" s="12" t="n">
         <v>33445</v>
+      </c>
+      <c r="Q120" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -5050,77 +6027,99 @@
         <v>2010</v>
       </c>
       <c r="F121" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G121" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H121" s="7" t="n">
+        <v>1341</v>
+      </c>
+      <c r="I121" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G121" s="7" t="n">
-        <v>1341</v>
-      </c>
-      <c r="H121" s="7" t="n">
+      <c r="J121" s="7" t="n">
         <v>887</v>
       </c>
-      <c r="I121" s="7" t="n">
+      <c r="K121" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="J121" s="7" t="n">
+      <c r="L121" s="7" t="n">
         <v>106</v>
       </c>
-      <c r="K121" s="7" t="n">
+      <c r="M121" s="7" t="n">
         <v>201</v>
       </c>
-      <c r="L121" s="7" t="n">
+      <c r="N121" s="7" t="n">
         <v>239</v>
       </c>
-      <c r="M121" s="6" t="n">
+      <c r="O121" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="N121" s="7" t="n">
+      <c r="P121" s="7" t="n">
         <v>287446</v>
       </c>
+      <c r="Q121" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="6" t="inlineStr">
+      <c r="A122" s="11" t="inlineStr">
         <is>
           <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
         </is>
       </c>
-      <c r="B122" s="6" t="n">
+      <c r="B122" s="11" t="n">
         <v>437776835</v>
       </c>
-      <c r="C122" s="7" t="n">
+      <c r="C122" s="12" t="n">
         <v>819.72</v>
       </c>
-      <c r="D122" s="6" t="n">
+      <c r="D122" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E122" s="7" t="n">
+      <c r="E122" s="12" t="n">
+        <v>2323</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G122" s="12" t="n">
         <v>2834</v>
       </c>
-      <c r="F122" s="6" t="n">
+      <c r="H122" s="12" t="n">
+        <v>1890</v>
+      </c>
+      <c r="I122" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G122" s="7" t="n">
-        <v>1890</v>
-      </c>
-      <c r="H122" s="7" t="n">
+      <c r="J122" s="12" t="n">
         <v>1276</v>
       </c>
-      <c r="I122" s="7" t="n">
+      <c r="K122" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="J122" s="7" t="n">
+      <c r="L122" s="12" t="n">
         <v>159</v>
       </c>
-      <c r="K122" s="7" t="n">
+      <c r="M122" s="12" t="n">
         <v>283</v>
       </c>
-      <c r="L122" s="7" t="n">
+      <c r="N122" s="12" t="n">
         <v>246</v>
       </c>
-      <c r="M122" s="6" t="n">
+      <c r="O122" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N122" s="7" t="n">
+      <c r="P122" s="12" t="n">
         <v>1230</v>
+      </c>
+      <c r="Q122" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -5142,31 +6141,42 @@
         <v>2262</v>
       </c>
       <c r="F123" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="G123" s="7" t="n">
+        <v>2262</v>
+      </c>
+      <c r="H123" s="7" t="n">
+        <v>1509</v>
+      </c>
+      <c r="I123" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G123" s="7" t="n">
-        <v>1509</v>
-      </c>
-      <c r="H123" s="7" t="n">
+      <c r="J123" s="7" t="n">
         <v>1002</v>
       </c>
-      <c r="I123" s="7" t="n">
+      <c r="K123" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="J123" s="7" t="n">
+      <c r="L123" s="7" t="n">
         <v>126</v>
       </c>
-      <c r="K123" s="7" t="n">
+      <c r="M123" s="7" t="n">
         <v>226</v>
       </c>
-      <c r="L123" s="7" t="n">
+      <c r="N123" s="7" t="n">
         <v>369</v>
       </c>
-      <c r="M123" s="6" t="n">
+      <c r="O123" s="6" t="n">
         <v>76</v>
       </c>
-      <c r="N123" s="7" t="n">
+      <c r="P123" s="7" t="n">
         <v>296069</v>
+      </c>
+      <c r="Q123" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -5191,9 +6201,12 @@
       <c r="K124" s="9" t="n"/>
       <c r="L124" s="9" t="n"/>
       <c r="M124" s="9" t="n"/>
-      <c r="N124" s="10" t="n">
+      <c r="N124" s="9" t="n"/>
+      <c r="O124" s="9" t="n"/>
+      <c r="P124" s="10" t="n">
         <v>1382315</v>
       </c>
+      <c r="Q124" s="9" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -5214,6 +6227,9 @@
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="5" t="n"/>
       <c r="N125" s="5" t="n"/>
+      <c r="O125" s="5" t="n"/>
+      <c r="P125" s="5" t="n"/>
+      <c r="Q125" s="5" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
@@ -5234,31 +6250,42 @@
         <v>2166</v>
       </c>
       <c r="F126" s="6" t="n">
+        <v>121</v>
+      </c>
+      <c r="G126" s="7" t="n">
+        <v>2166</v>
+      </c>
+      <c r="H126" s="7" t="n">
+        <v>1445</v>
+      </c>
+      <c r="I126" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G126" s="7" t="n">
-        <v>1445</v>
-      </c>
-      <c r="H126" s="7" t="n">
+      <c r="J126" s="7" t="n">
         <v>963</v>
       </c>
-      <c r="I126" s="7" t="n">
+      <c r="K126" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="J126" s="7" t="n">
+      <c r="L126" s="7" t="n">
         <v>128</v>
       </c>
-      <c r="K126" s="7" t="n">
+      <c r="M126" s="7" t="n">
         <v>217</v>
       </c>
-      <c r="L126" s="7" t="n">
+      <c r="N126" s="7" t="n">
         <v>444</v>
       </c>
-      <c r="M126" s="6" t="n">
+      <c r="O126" s="6" t="n">
         <v>121</v>
       </c>
-      <c r="N126" s="7" t="n">
+      <c r="P126" s="7" t="n">
         <v>13330</v>
+      </c>
+      <c r="Q126" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -5280,31 +6307,42 @@
         <v>1543</v>
       </c>
       <c r="F127" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="G127" s="7" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H127" s="7" t="n">
+        <v>1029</v>
+      </c>
+      <c r="I127" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G127" s="7" t="n">
-        <v>1029</v>
-      </c>
-      <c r="H127" s="7" t="n">
+      <c r="J127" s="7" t="n">
         <v>682</v>
       </c>
-      <c r="I127" s="7" t="n">
+      <c r="K127" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="J127" s="7" t="n">
+      <c r="L127" s="7" t="n">
         <v>84</v>
       </c>
-      <c r="K127" s="7" t="n">
+      <c r="M127" s="7" t="n">
         <v>154</v>
       </c>
-      <c r="L127" s="7" t="n">
+      <c r="N127" s="7" t="n">
         <v>267</v>
       </c>
-      <c r="M127" s="6" t="n">
+      <c r="O127" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="N127" s="7" t="n">
+      <c r="P127" s="7" t="n">
         <v>5880</v>
+      </c>
+      <c r="Q127" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -5329,9 +6367,12 @@
       <c r="K128" s="9" t="n"/>
       <c r="L128" s="9" t="n"/>
       <c r="M128" s="9" t="n"/>
-      <c r="N128" s="10" t="n">
+      <c r="N128" s="9" t="n"/>
+      <c r="O128" s="9" t="n"/>
+      <c r="P128" s="10" t="n">
         <v>19210</v>
       </c>
+      <c r="Q128" s="9" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -5352,97 +6393,122 @@
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="5" t="n"/>
       <c r="N129" s="5" t="n"/>
+      <c r="O129" s="5" t="n"/>
+      <c r="P129" s="5" t="n"/>
+      <c r="Q129" s="5" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="6" t="inlineStr">
+      <c r="A130" s="11" t="inlineStr">
         <is>
           <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cleansing Bar [106g] / Мыло для проблемной кожи с aha bha кислотами</t>
         </is>
       </c>
-      <c r="B130" s="6" t="n">
+      <c r="B130" s="11" t="n">
         <v>248928046</v>
       </c>
-      <c r="C130" s="7" t="n">
+      <c r="C130" s="12" t="n">
         <v>549.71</v>
       </c>
-      <c r="D130" s="6" t="n">
+      <c r="D130" s="11" t="n">
         <v>525</v>
       </c>
-      <c r="E130" s="7" t="n">
+      <c r="E130" s="12" t="n">
+        <v>1854</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G130" s="12" t="n">
         <v>1930</v>
       </c>
-      <c r="F130" s="6" t="n">
+      <c r="H130" s="12" t="n">
+        <v>1287</v>
+      </c>
+      <c r="I130" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G130" s="7" t="n">
-        <v>1287</v>
-      </c>
-      <c r="H130" s="7" t="n">
+      <c r="J130" s="12" t="n">
         <v>846</v>
       </c>
-      <c r="I130" s="7" t="n">
+      <c r="K130" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="J130" s="7" t="n">
+      <c r="L130" s="12" t="n">
         <v>128</v>
       </c>
-      <c r="K130" s="7" t="n">
+      <c r="M130" s="12" t="n">
         <v>193</v>
       </c>
-      <c r="L130" s="7" t="n">
+      <c r="N130" s="12" t="n">
         <v>165</v>
       </c>
-      <c r="M130" s="6" t="n">
+      <c r="O130" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N130" s="7" t="n">
+      <c r="P130" s="12" t="n">
         <v>86579</v>
       </c>
+      <c r="Q130" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="6" t="inlineStr">
+      <c r="A131" s="11" t="inlineStr">
         <is>
           <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
         </is>
       </c>
-      <c r="B131" s="6" t="n">
+      <c r="B131" s="11" t="n">
         <v>248929125</v>
       </c>
-      <c r="C131" s="7" t="n">
+      <c r="C131" s="12" t="n">
         <v>1057.2</v>
       </c>
-      <c r="D131" s="6" t="n">
+      <c r="D131" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="E131" s="7" t="n">
+      <c r="E131" s="12" t="n">
+        <v>3257</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G131" s="12" t="n">
         <v>3572</v>
       </c>
-      <c r="F131" s="6" t="n">
+      <c r="H131" s="12" t="n">
+        <v>2382</v>
+      </c>
+      <c r="I131" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G131" s="7" t="n">
-        <v>2382</v>
-      </c>
-      <c r="H131" s="7" t="n">
+      <c r="J131" s="12" t="n">
         <v>1575</v>
       </c>
-      <c r="I131" s="7" t="n">
+      <c r="K131" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="J131" s="7" t="n">
+      <c r="L131" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="K131" s="7" t="n">
+      <c r="M131" s="12" t="n">
         <v>357</v>
       </c>
-      <c r="L131" s="7" t="n">
+      <c r="N131" s="12" t="n">
         <v>317</v>
       </c>
-      <c r="M131" s="6" t="n">
+      <c r="O131" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N131" s="7" t="n">
+      <c r="P131" s="12" t="n">
         <v>17444</v>
+      </c>
+      <c r="Q131" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -5467,9 +6533,12 @@
       <c r="K132" s="9" t="n"/>
       <c r="L132" s="9" t="n"/>
       <c r="M132" s="9" t="n"/>
-      <c r="N132" s="10" t="n">
+      <c r="N132" s="9" t="n"/>
+      <c r="O132" s="9" t="n"/>
+      <c r="P132" s="10" t="n">
         <v>104023</v>
       </c>
+      <c r="Q132" s="9" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -5490,51 +6559,65 @@
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="5" t="n"/>
       <c r="N133" s="5" t="n"/>
+      <c r="O133" s="5" t="n"/>
+      <c r="P133" s="5" t="n"/>
+      <c r="Q133" s="5" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="6" t="inlineStr">
+      <c r="A134" s="11" t="inlineStr">
         <is>
           <t>THE ORDINARY - Argireline Solution 10% [30ml] / Сыворотка для лица от прыщей и акне с ниацинамидом 10 %</t>
         </is>
       </c>
-      <c r="B134" s="6" t="n">
+      <c r="B134" s="11" t="n">
         <v>214312385</v>
       </c>
-      <c r="C134" s="7" t="n">
+      <c r="C134" s="12" t="n">
         <v>722.04</v>
       </c>
-      <c r="D134" s="6" t="n">
+      <c r="D134" s="11" t="n">
         <v>115</v>
       </c>
-      <c r="E134" s="7" t="n">
+      <c r="E134" s="12" t="n">
+        <v>2166</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="G134" s="12" t="n">
         <v>2455</v>
       </c>
-      <c r="F134" s="6" t="n">
+      <c r="H134" s="12" t="n">
+        <v>1637</v>
+      </c>
+      <c r="I134" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G134" s="7" t="n">
-        <v>1637</v>
-      </c>
-      <c r="H134" s="7" t="n">
+      <c r="J134" s="12" t="n">
         <v>1092</v>
       </c>
-      <c r="I134" s="7" t="n">
+      <c r="K134" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="J134" s="7" t="n">
+      <c r="L134" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="K134" s="7" t="n">
+      <c r="M134" s="12" t="n">
         <v>246</v>
       </c>
-      <c r="L134" s="7" t="n">
+      <c r="N134" s="12" t="n">
         <v>217</v>
       </c>
-      <c r="M134" s="6" t="n">
+      <c r="O134" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N134" s="7" t="n">
+      <c r="P134" s="12" t="n">
         <v>24910</v>
+      </c>
+      <c r="Q134" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -5556,31 +6639,42 @@
         <v>2944</v>
       </c>
       <c r="F135" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="G135" s="7" t="n">
+        <v>2944</v>
+      </c>
+      <c r="H135" s="7" t="n">
+        <v>1964</v>
+      </c>
+      <c r="I135" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G135" s="7" t="n">
-        <v>1964</v>
-      </c>
-      <c r="H135" s="7" t="n">
+      <c r="J135" s="7" t="n">
         <v>1298</v>
       </c>
-      <c r="I135" s="7" t="n">
+      <c r="K135" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="J135" s="7" t="n">
+      <c r="L135" s="7" t="n">
         <v>167</v>
       </c>
-      <c r="K135" s="7" t="n">
+      <c r="M135" s="7" t="n">
         <v>294</v>
       </c>
-      <c r="L135" s="7" t="n">
+      <c r="N135" s="7" t="n">
         <v>278</v>
       </c>
-      <c r="M135" s="6" t="n">
+      <c r="O135" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="N135" s="7" t="n">
+      <c r="P135" s="7" t="n">
         <v>6949</v>
+      </c>
+      <c r="Q135" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -5605,9 +6699,12 @@
       <c r="K136" s="9" t="n"/>
       <c r="L136" s="9" t="n"/>
       <c r="M136" s="9" t="n"/>
-      <c r="N136" s="10" t="n">
+      <c r="N136" s="9" t="n"/>
+      <c r="O136" s="9" t="n"/>
+      <c r="P136" s="10" t="n">
         <v>31859</v>
       </c>
+      <c r="Q136" s="9" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -5628,97 +6725,122 @@
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="5" t="n"/>
       <c r="N137" s="5" t="n"/>
+      <c r="O137" s="5" t="n"/>
+      <c r="P137" s="5" t="n"/>
+      <c r="Q137" s="5" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="6" t="inlineStr">
+      <c r="A138" s="11" t="inlineStr">
         <is>
           <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
         </is>
       </c>
-      <c r="B138" s="6" t="n">
+      <c r="B138" s="11" t="n">
         <v>868516027</v>
       </c>
-      <c r="C138" s="7" t="n">
+      <c r="C138" s="12" t="n">
         <v>663.86</v>
       </c>
-      <c r="D138" s="6" t="n">
+      <c r="D138" s="11" t="n">
         <v>15980</v>
       </c>
-      <c r="E138" s="7" t="n">
+      <c r="E138" s="12" t="n">
+        <v>2280</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="G138" s="12" t="n">
         <v>2377</v>
       </c>
-      <c r="F138" s="6" t="n">
+      <c r="H138" s="12" t="n">
+        <v>1586</v>
+      </c>
+      <c r="I138" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G138" s="7" t="n">
-        <v>1586</v>
-      </c>
-      <c r="H138" s="7" t="n">
+      <c r="J138" s="12" t="n">
         <v>1056</v>
       </c>
-      <c r="I138" s="7" t="n">
+      <c r="K138" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="J138" s="7" t="n">
+      <c r="L138" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="K138" s="7" t="n">
+      <c r="M138" s="12" t="n">
         <v>238</v>
       </c>
-      <c r="L138" s="7" t="n">
+      <c r="N138" s="12" t="n">
         <v>199</v>
       </c>
-      <c r="M138" s="6" t="n">
+      <c r="O138" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N138" s="7" t="n">
+      <c r="P138" s="12" t="n">
         <v>3182545</v>
       </c>
+      <c r="Q138" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="6" t="inlineStr">
+      <c r="A139" s="11" t="inlineStr">
         <is>
           <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
         </is>
       </c>
-      <c r="B139" s="6" t="n">
+      <c r="B139" s="11" t="n">
         <v>551387355</v>
       </c>
-      <c r="C139" s="7" t="n">
+      <c r="C139" s="12" t="n">
         <v>512.1799999999999</v>
       </c>
-      <c r="D139" s="6" t="n">
+      <c r="D139" s="11" t="n">
         <v>8728</v>
       </c>
-      <c r="E139" s="7" t="n">
+      <c r="E139" s="12" t="n">
+        <v>1698</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="G139" s="12" t="n">
         <v>1780</v>
       </c>
-      <c r="F139" s="6" t="n">
+      <c r="H139" s="12" t="n">
+        <v>1187</v>
+      </c>
+      <c r="I139" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G139" s="7" t="n">
-        <v>1187</v>
-      </c>
-      <c r="H139" s="7" t="n">
+      <c r="J139" s="12" t="n">
         <v>787</v>
       </c>
-      <c r="I139" s="7" t="n">
+      <c r="K139" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="J139" s="7" t="n">
+      <c r="L139" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="K139" s="7" t="n">
+      <c r="M139" s="12" t="n">
         <v>178</v>
       </c>
-      <c r="L139" s="7" t="n">
+      <c r="N139" s="12" t="n">
         <v>154</v>
       </c>
-      <c r="M139" s="6" t="n">
+      <c r="O139" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N139" s="7" t="n">
+      <c r="P139" s="12" t="n">
         <v>1341092</v>
+      </c>
+      <c r="Q139" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -5740,31 +6862,42 @@
         <v>2166</v>
       </c>
       <c r="F140" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G140" s="7" t="n">
+        <v>2166</v>
+      </c>
+      <c r="H140" s="7" t="n">
+        <v>1445</v>
+      </c>
+      <c r="I140" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G140" s="7" t="n">
-        <v>1445</v>
-      </c>
-      <c r="H140" s="7" t="n">
+      <c r="J140" s="7" t="n">
         <v>967</v>
       </c>
-      <c r="I140" s="7" t="n">
+      <c r="K140" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="J140" s="7" t="n">
+      <c r="L140" s="7" t="n">
         <v>115</v>
       </c>
-      <c r="K140" s="7" t="n">
+      <c r="M140" s="7" t="n">
         <v>217</v>
       </c>
-      <c r="L140" s="7" t="n">
+      <c r="N140" s="7" t="n">
         <v>291</v>
       </c>
-      <c r="M140" s="6" t="n">
+      <c r="O140" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="N140" s="7" t="n">
+      <c r="P140" s="7" t="n">
         <v>646033</v>
+      </c>
+      <c r="Q140" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="141">
@@ -5786,31 +6919,42 @@
         <v>610</v>
       </c>
       <c r="F141" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="G141" s="7" t="n">
+        <v>610</v>
+      </c>
+      <c r="H141" s="7" t="n">
+        <v>406</v>
+      </c>
+      <c r="I141" s="6" t="n">
         <v>33.5</v>
       </c>
-      <c r="G141" s="7" t="n">
-        <v>406</v>
-      </c>
-      <c r="H141" s="7" t="n">
+      <c r="J141" s="7" t="n">
         <v>269</v>
       </c>
-      <c r="I141" s="7" t="n">
+      <c r="K141" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="J141" s="7" t="n">
+      <c r="L141" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="K141" s="7" t="n">
+      <c r="M141" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="L141" s="7" t="n">
+      <c r="N141" s="7" t="n">
         <v>105</v>
       </c>
-      <c r="M141" s="6" t="n">
+      <c r="O141" s="6" t="n">
         <v>108</v>
       </c>
-      <c r="N141" s="7" t="n">
+      <c r="P141" s="7" t="n">
         <v>135963</v>
+      </c>
+      <c r="Q141" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -5832,169 +6976,213 @@
         <v>2789</v>
       </c>
       <c r="F142" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="G142" s="7" t="n">
+        <v>2789</v>
+      </c>
+      <c r="H142" s="7" t="n">
+        <v>1860</v>
+      </c>
+      <c r="I142" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G142" s="7" t="n">
-        <v>1860</v>
-      </c>
-      <c r="H142" s="7" t="n">
+      <c r="J142" s="7" t="n">
         <v>1226</v>
       </c>
-      <c r="I142" s="7" t="n">
+      <c r="K142" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="J142" s="7" t="n">
+      <c r="L142" s="7" t="n">
         <v>137</v>
       </c>
-      <c r="K142" s="7" t="n">
+      <c r="M142" s="7" t="n">
         <v>279</v>
       </c>
-      <c r="L142" s="7" t="n">
+      <c r="N142" s="7" t="n">
         <v>463</v>
       </c>
-      <c r="M142" s="6" t="n">
+      <c r="O142" s="6" t="n">
         <v>74</v>
       </c>
-      <c r="N142" s="7" t="n">
+      <c r="P142" s="7" t="n">
         <v>6020</v>
       </c>
+      <c r="Q142" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
-      <c r="A143" s="6" t="inlineStr">
+      <c r="A143" s="11" t="inlineStr">
         <is>
           <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
         </is>
       </c>
-      <c r="B143" s="6" t="n">
+      <c r="B143" s="11" t="n">
         <v>551392965</v>
       </c>
-      <c r="C143" s="7" t="n">
+      <c r="C143" s="12" t="n">
         <v>864.11</v>
       </c>
-      <c r="D143" s="6" t="n">
+      <c r="D143" s="11" t="n">
         <v>353</v>
       </c>
-      <c r="E143" s="7" t="n">
+      <c r="E143" s="12" t="n">
+        <v>2944</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="G143" s="12" t="n">
         <v>2949</v>
       </c>
-      <c r="F143" s="6" t="n">
+      <c r="H143" s="12" t="n">
+        <v>1967</v>
+      </c>
+      <c r="I143" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G143" s="7" t="n">
-        <v>1967</v>
-      </c>
-      <c r="H143" s="7" t="n">
+      <c r="J143" s="12" t="n">
         <v>1310</v>
       </c>
-      <c r="I143" s="7" t="n">
+      <c r="K143" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="J143" s="7" t="n">
+      <c r="L143" s="12" t="n">
         <v>168</v>
       </c>
-      <c r="K143" s="7" t="n">
+      <c r="M143" s="12" t="n">
         <v>295</v>
       </c>
-      <c r="L143" s="7" t="n">
+      <c r="N143" s="12" t="n">
         <v>259</v>
       </c>
-      <c r="M143" s="6" t="n">
+      <c r="O143" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N143" s="7" t="n">
+      <c r="P143" s="12" t="n">
         <v>91509</v>
       </c>
+      <c r="Q143" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" s="6" t="inlineStr">
+      <c r="A144" s="11" t="inlineStr">
         <is>
           <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
         </is>
       </c>
-      <c r="B144" s="6" t="n">
+      <c r="B144" s="11" t="n">
         <v>551607905</v>
       </c>
-      <c r="C144" s="7" t="n">
+      <c r="C144" s="12" t="n">
         <v>707.88</v>
       </c>
-      <c r="D144" s="6" t="n">
+      <c r="D144" s="11" t="n">
         <v>1456</v>
       </c>
-      <c r="E144" s="7" t="n">
+      <c r="E144" s="12" t="n">
+        <v>2323</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="G144" s="12" t="n">
         <v>2428</v>
       </c>
-      <c r="F144" s="6" t="n">
+      <c r="H144" s="12" t="n">
+        <v>1620</v>
+      </c>
+      <c r="I144" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G144" s="7" t="n">
-        <v>1620</v>
-      </c>
-      <c r="H144" s="7" t="n">
+      <c r="J144" s="12" t="n">
         <v>1082</v>
       </c>
-      <c r="I144" s="7" t="n">
+      <c r="K144" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="J144" s="7" t="n">
+      <c r="L144" s="12" t="n">
         <v>128</v>
       </c>
-      <c r="K144" s="7" t="n">
+      <c r="M144" s="12" t="n">
         <v>243</v>
       </c>
-      <c r="L144" s="7" t="n">
+      <c r="N144" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="M144" s="6" t="n">
+      <c r="O144" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N144" s="7" t="n">
+      <c r="P144" s="12" t="n">
         <v>309202</v>
       </c>
+      <c r="Q144" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
+      </c>
     </row>
     <row r="145">
-      <c r="A145" s="6" t="inlineStr">
+      <c r="A145" s="11" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
         </is>
       </c>
-      <c r="B145" s="6" t="n">
+      <c r="B145" s="11" t="n">
         <v>551472457</v>
       </c>
-      <c r="C145" s="7" t="n">
+      <c r="C145" s="12" t="n">
         <v>763.83</v>
       </c>
-      <c r="D145" s="6" t="n">
+      <c r="D145" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="E145" s="7" t="n">
+      <c r="E145" s="12" t="n">
+        <v>2478</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="G145" s="12" t="n">
         <v>2640</v>
       </c>
-      <c r="F145" s="6" t="n">
+      <c r="H145" s="12" t="n">
+        <v>1761</v>
+      </c>
+      <c r="I145" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G145" s="7" t="n">
-        <v>1761</v>
-      </c>
-      <c r="H145" s="7" t="n">
+      <c r="J145" s="12" t="n">
         <v>1171</v>
       </c>
-      <c r="I145" s="7" t="n">
+      <c r="K145" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="J145" s="7" t="n">
+      <c r="L145" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="K145" s="7" t="n">
+      <c r="M145" s="12" t="n">
         <v>264</v>
       </c>
-      <c r="L145" s="7" t="n">
+      <c r="N145" s="12" t="n">
         <v>229</v>
       </c>
-      <c r="M145" s="6" t="n">
+      <c r="O145" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N145" s="7" t="n">
+      <c r="P145" s="12" t="n">
         <v>8020</v>
+      </c>
+      <c r="Q145" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -6016,31 +7204,42 @@
         <v>2167</v>
       </c>
       <c r="F146" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="G146" s="7" t="n">
+        <v>2167</v>
+      </c>
+      <c r="H146" s="7" t="n">
+        <v>1445</v>
+      </c>
+      <c r="I146" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G146" s="7" t="n">
-        <v>1445</v>
-      </c>
-      <c r="H146" s="7" t="n">
+      <c r="J146" s="7" t="n">
         <v>959</v>
       </c>
-      <c r="I146" s="7" t="n">
+      <c r="K146" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="J146" s="7" t="n">
+      <c r="L146" s="7" t="n">
         <v>119</v>
       </c>
-      <c r="K146" s="7" t="n">
+      <c r="M146" s="7" t="n">
         <v>217</v>
       </c>
-      <c r="L146" s="7" t="n">
+      <c r="N146" s="7" t="n">
         <v>255</v>
       </c>
-      <c r="M146" s="6" t="n">
+      <c r="O146" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="N146" s="7" t="n">
+      <c r="P146" s="7" t="n">
         <v>350172</v>
+      </c>
+      <c r="Q146" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -6062,77 +7261,99 @@
         <v>2634</v>
       </c>
       <c r="F147" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G147" s="7" t="n">
+        <v>2634</v>
+      </c>
+      <c r="H147" s="7" t="n">
+        <v>1757</v>
+      </c>
+      <c r="I147" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="G147" s="7" t="n">
-        <v>1757</v>
-      </c>
-      <c r="H147" s="7" t="n">
+      <c r="J147" s="7" t="n">
         <v>1167</v>
       </c>
-      <c r="I147" s="7" t="n">
+      <c r="K147" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="J147" s="7" t="n">
+      <c r="L147" s="7" t="n">
         <v>147</v>
       </c>
-      <c r="K147" s="7" t="n">
+      <c r="M147" s="7" t="n">
         <v>263</v>
       </c>
-      <c r="L147" s="7" t="n">
+      <c r="N147" s="7" t="n">
         <v>308</v>
       </c>
-      <c r="M147" s="6" t="n">
+      <c r="O147" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="N147" s="7" t="n">
+      <c r="P147" s="7" t="n">
         <v>23701</v>
       </c>
+      <c r="Q147" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
+        </is>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="6" t="inlineStr">
+      <c r="A148" s="11" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
         </is>
       </c>
-      <c r="B148" s="6" t="n">
+      <c r="B148" s="11" t="n">
         <v>551518955</v>
       </c>
-      <c r="C148" s="7" t="n">
+      <c r="C148" s="12" t="n">
         <v>719.58</v>
       </c>
-      <c r="D148" s="6" t="n">
+      <c r="D148" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="E148" s="7" t="n">
+      <c r="E148" s="12" t="n">
+        <v>2479</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="G148" s="12" t="n">
         <v>2515</v>
       </c>
-      <c r="F148" s="6" t="n">
+      <c r="H148" s="12" t="n">
+        <v>1678</v>
+      </c>
+      <c r="I148" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G148" s="7" t="n">
-        <v>1678</v>
-      </c>
-      <c r="H148" s="7" t="n">
+      <c r="J148" s="12" t="n">
         <v>1130</v>
       </c>
-      <c r="I148" s="7" t="n">
+      <c r="K148" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="J148" s="7" t="n">
+      <c r="L148" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="K148" s="7" t="n">
+      <c r="M148" s="12" t="n">
         <v>252</v>
       </c>
-      <c r="L148" s="7" t="n">
+      <c r="N148" s="12" t="n">
         <v>216</v>
       </c>
-      <c r="M148" s="6" t="n">
+      <c r="O148" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N148" s="7" t="n">
+      <c r="P148" s="12" t="n">
         <v>5181</v>
+      </c>
+      <c r="Q148" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -6157,9 +7378,12 @@
       <c r="K149" s="9" t="n"/>
       <c r="L149" s="9" t="n"/>
       <c r="M149" s="9" t="n"/>
-      <c r="N149" s="10" t="n">
+      <c r="N149" s="9" t="n"/>
+      <c r="O149" s="9" t="n"/>
+      <c r="P149" s="10" t="n">
         <v>6099438</v>
       </c>
+      <c r="Q149" s="9" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -6180,97 +7404,122 @@
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="5" t="n"/>
       <c r="N150" s="5" t="n"/>
+      <c r="O150" s="5" t="n"/>
+      <c r="P150" s="5" t="n"/>
+      <c r="Q150" s="5" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="6" t="inlineStr">
+      <c r="A151" s="11" t="inlineStr">
         <is>
           <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
         </is>
       </c>
-      <c r="B151" s="6" t="n">
+      <c r="B151" s="11" t="n">
         <v>1119249556</v>
       </c>
-      <c r="C151" s="7" t="n">
+      <c r="C151" s="12" t="n">
         <v>1335.95</v>
       </c>
-      <c r="D151" s="6" t="n">
+      <c r="D151" s="11" t="n">
         <v>1008</v>
       </c>
-      <c r="E151" s="7" t="n">
+      <c r="E151" s="12" t="n">
+        <v>3591</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G151" s="12" t="n">
         <v>4443</v>
       </c>
-      <c r="F151" s="6" t="n">
+      <c r="H151" s="12" t="n">
+        <v>2964</v>
+      </c>
+      <c r="I151" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G151" s="7" t="n">
-        <v>2964</v>
-      </c>
-      <c r="H151" s="7" t="n">
+      <c r="J151" s="12" t="n">
         <v>1963</v>
       </c>
-      <c r="I151" s="7" t="n">
+      <c r="K151" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="J151" s="7" t="n">
+      <c r="L151" s="12" t="n">
         <v>239</v>
       </c>
-      <c r="K151" s="7" t="n">
+      <c r="M151" s="12" t="n">
         <v>444</v>
       </c>
-      <c r="L151" s="7" t="n">
+      <c r="N151" s="12" t="n">
         <v>401</v>
       </c>
-      <c r="M151" s="6" t="n">
+      <c r="O151" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N151" s="7" t="n">
+      <c r="P151" s="12" t="n">
         <v>403991</v>
       </c>
+      <c r="Q151" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" s="6" t="inlineStr">
+      <c r="A152" s="11" t="inlineStr">
         <is>
           <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
         </is>
       </c>
-      <c r="B152" s="6" t="n">
+      <c r="B152" s="11" t="n">
         <v>1123494802</v>
       </c>
-      <c r="C152" s="7" t="n">
+      <c r="C152" s="12" t="n">
         <v>974.04</v>
       </c>
-      <c r="D152" s="6" t="n">
+      <c r="D152" s="11" t="n">
         <v>397</v>
       </c>
-      <c r="E152" s="7" t="n">
+      <c r="E152" s="12" t="n">
+        <v>2241</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>-11</v>
+      </c>
+      <c r="G152" s="12" t="n">
         <v>3221</v>
       </c>
-      <c r="F152" s="6" t="n">
+      <c r="H152" s="12" t="n">
+        <v>2148</v>
+      </c>
+      <c r="I152" s="11" t="n">
         <v>33.3</v>
       </c>
-      <c r="G152" s="7" t="n">
-        <v>2148</v>
-      </c>
-      <c r="H152" s="7" t="n">
+      <c r="J152" s="12" t="n">
         <v>1422</v>
       </c>
-      <c r="I152" s="7" t="n">
+      <c r="K152" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="J152" s="7" t="n">
+      <c r="L152" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="K152" s="7" t="n">
+      <c r="M152" s="12" t="n">
         <v>322</v>
       </c>
-      <c r="L152" s="7" t="n">
+      <c r="N152" s="12" t="n">
         <v>292</v>
       </c>
-      <c r="M152" s="6" t="n">
+      <c r="O152" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N152" s="7" t="n">
+      <c r="P152" s="12" t="n">
         <v>116008</v>
+      </c>
+      <c r="Q152" s="11" t="inlineStr">
+        <is>
+          <t>Поднять цену</t>
+        </is>
       </c>
     </row>
     <row r="153">
@@ -6295,38 +7544,44 @@
       <c r="K153" s="9" t="n"/>
       <c r="L153" s="9" t="n"/>
       <c r="M153" s="9" t="n"/>
-      <c r="N153" s="10" t="n">
+      <c r="N153" s="9" t="n"/>
+      <c r="O153" s="9" t="n"/>
+      <c r="P153" s="10" t="n">
         <v>519999</v>
       </c>
+      <c r="Q153" s="9" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="11" t="inlineStr">
+      <c r="A155" s="13" t="inlineStr">
         <is>
           <t>ИТОГО ПО ВСЕМ БРЕНДАМ</t>
         </is>
       </c>
-      <c r="B155" s="12" t="n"/>
-      <c r="C155" s="13" t="n">
+      <c r="B155" s="14" t="n"/>
+      <c r="C155" s="15" t="n">
         <v>47463088</v>
       </c>
-      <c r="D155" s="13" t="n">
+      <c r="D155" s="15" t="n">
         <v>107901</v>
       </c>
-      <c r="E155" s="12" t="n"/>
-      <c r="F155" s="12" t="n"/>
-      <c r="G155" s="12" t="n"/>
-      <c r="H155" s="12" t="n"/>
-      <c r="I155" s="12" t="n"/>
-      <c r="J155" s="12" t="n"/>
-      <c r="K155" s="12" t="n"/>
-      <c r="L155" s="12" t="n"/>
-      <c r="M155" s="12" t="n"/>
-      <c r="N155" s="13" t="n">
+      <c r="E155" s="14" t="n"/>
+      <c r="F155" s="14" t="n"/>
+      <c r="G155" s="14" t="n"/>
+      <c r="H155" s="14" t="n"/>
+      <c r="I155" s="14" t="n"/>
+      <c r="J155" s="14" t="n"/>
+      <c r="K155" s="14" t="n"/>
+      <c r="L155" s="14" t="n"/>
+      <c r="M155" s="14" t="n"/>
+      <c r="N155" s="14" t="n"/>
+      <c r="O155" s="14" t="n"/>
+      <c r="P155" s="15" t="n">
         <v>20833752</v>
       </c>
+      <c r="Q155" s="14" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="14" t="inlineStr">
+      <c r="A156" s="16" t="inlineStr">
         <is>
           <t>Себестоимость остатков: 47.46 млн ₽   |   Потенциальный заработок при ROI≥30%: 20.83 млн ₽   |   Остаток: 107,901 шт</t>
         </is>
